--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123398345</v>
+        <v>123403597</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>78414</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494856</v>
+        <v>494804</v>
       </c>
       <c r="R2" t="n">
-        <v>6847291</v>
+        <v>6847196</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123397886</v>
+        <v>123395906</v>
       </c>
       <c r="B3" t="n">
-        <v>79848</v>
+        <v>78769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494832</v>
+        <v>494732</v>
       </c>
       <c r="R3" t="n">
-        <v>6847342</v>
+        <v>6847579</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123399650</v>
+        <v>123396228</v>
       </c>
       <c r="B4" t="n">
-        <v>79876</v>
+        <v>79358</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494916</v>
+        <v>494766</v>
       </c>
       <c r="R4" t="n">
-        <v>6847423</v>
+        <v>6847564</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123398359</v>
+        <v>123397886</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494882</v>
+        <v>494832</v>
       </c>
       <c r="R5" t="n">
-        <v>6847247</v>
+        <v>6847342</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123403076</v>
+        <v>123396986</v>
       </c>
       <c r="B6" t="n">
-        <v>79876</v>
+        <v>78506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494829</v>
+        <v>494778</v>
       </c>
       <c r="R6" t="n">
-        <v>6847079</v>
+        <v>6847448</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123398134</v>
+        <v>123399373</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,17 +1221,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494855</v>
+        <v>494944</v>
       </c>
       <c r="R7" t="n">
-        <v>6847271</v>
+        <v>6847470</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123396228</v>
+        <v>123398345</v>
       </c>
       <c r="B8" t="n">
-        <v>79355</v>
+        <v>78769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,37 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494766</v>
+        <v>494856</v>
       </c>
       <c r="R8" t="n">
-        <v>6847564</v>
+        <v>6847291</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123402474</v>
+        <v>123397955</v>
       </c>
       <c r="B9" t="n">
-        <v>90952</v>
+        <v>78506</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,37 +1405,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494859</v>
+        <v>494834</v>
       </c>
       <c r="R9" t="n">
-        <v>6847114</v>
+        <v>6847337</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123398038</v>
+        <v>123399860</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,17 +1527,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494836</v>
+        <v>494841</v>
       </c>
       <c r="R10" t="n">
-        <v>6847308</v>
+        <v>6847322</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,22 +1581,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123403597</v>
+        <v>123399650</v>
       </c>
       <c r="B11" t="n">
-        <v>78411</v>
+        <v>79879</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494804</v>
+        <v>494916</v>
       </c>
       <c r="R11" t="n">
-        <v>6847196</v>
+        <v>6847423</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123395990</v>
+        <v>123398955</v>
       </c>
       <c r="B12" t="n">
-        <v>78502</v>
+        <v>78505</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494764</v>
+        <v>494898</v>
       </c>
       <c r="R12" t="n">
-        <v>6847568</v>
+        <v>6847337</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123402870</v>
+        <v>123398038</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494829</v>
+        <v>494836</v>
       </c>
       <c r="R13" t="n">
-        <v>6847079</v>
+        <v>6847308</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123402463</v>
+        <v>123403076</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>79879</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494846</v>
+        <v>494829</v>
       </c>
       <c r="R14" t="n">
-        <v>6847218</v>
+        <v>6847079</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123402561</v>
+        <v>123395955</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>78506</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,13 +2041,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494857</v>
+        <v>494764</v>
       </c>
       <c r="R15" t="n">
-        <v>6847085</v>
+        <v>6847568</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123395906</v>
+        <v>123395990</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>78505</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494732</v>
+        <v>494764</v>
       </c>
       <c r="R16" t="n">
-        <v>6847579</v>
+        <v>6847568</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2193,22 +2193,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123395626</v>
+        <v>123398723</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>78505</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,13 +2245,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494727</v>
+        <v>494908</v>
       </c>
       <c r="R17" t="n">
-        <v>6847673</v>
+        <v>6847305</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2295,22 +2295,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123399373</v>
+        <v>123395505</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>78506</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,37 +2323,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494944</v>
+        <v>494727</v>
       </c>
       <c r="R18" t="n">
-        <v>6847470</v>
+        <v>6847677</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2397,22 +2397,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123396986</v>
+        <v>123402845</v>
       </c>
       <c r="B19" t="n">
-        <v>78503</v>
+        <v>98368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,41 +2421,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494778</v>
+        <v>494845</v>
       </c>
       <c r="R19" t="n">
-        <v>6847448</v>
+        <v>6847104</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2499,22 +2508,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123399860</v>
+        <v>123402561</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>98368</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,41 +2532,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494841</v>
+        <v>494857</v>
       </c>
       <c r="R20" t="n">
-        <v>6847322</v>
+        <v>6847085</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2601,22 +2610,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123398955</v>
+        <v>123402870</v>
       </c>
       <c r="B21" t="n">
-        <v>78502</v>
+        <v>98368</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2634,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,13 +2662,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494898</v>
+        <v>494829</v>
       </c>
       <c r="R21" t="n">
-        <v>6847337</v>
+        <v>6847079</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2715,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123395955</v>
+        <v>123398134</v>
       </c>
       <c r="B22" t="n">
-        <v>78503</v>
+        <v>78769</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2740,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494764</v>
+        <v>494855</v>
       </c>
       <c r="R22" t="n">
-        <v>6847568</v>
+        <v>6847271</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2817,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123397955</v>
+        <v>123398359</v>
       </c>
       <c r="B23" t="n">
-        <v>78503</v>
+        <v>78769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,37 +2842,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494834</v>
+        <v>494882</v>
       </c>
       <c r="R23" t="n">
-        <v>6847337</v>
+        <v>6847247</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2907,22 +2916,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123402845</v>
+        <v>123396886</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>78414</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2931,47 +2940,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494845</v>
+        <v>494774</v>
       </c>
       <c r="R24" t="n">
-        <v>6847104</v>
+        <v>6847453</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,22 +3018,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123396886</v>
+        <v>123402463</v>
       </c>
       <c r="B25" t="n">
-        <v>78411</v>
+        <v>98368</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,25 +3042,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494774</v>
+        <v>494846</v>
       </c>
       <c r="R25" t="n">
-        <v>6847453</v>
+        <v>6847218</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123395505</v>
+        <v>123397848</v>
       </c>
       <c r="B26" t="n">
-        <v>78503</v>
+        <v>78414</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3148,21 +3148,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494727</v>
+        <v>494825</v>
       </c>
       <c r="R26" t="n">
-        <v>6847677</v>
+        <v>6847351</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123397848</v>
+        <v>123402474</v>
       </c>
       <c r="B27" t="n">
-        <v>78411</v>
+        <v>90955</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,13 +3274,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494825</v>
+        <v>494859</v>
       </c>
       <c r="R27" t="n">
-        <v>6847351</v>
+        <v>6847114</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123398723</v>
+        <v>123395626</v>
       </c>
       <c r="B28" t="n">
-        <v>78502</v>
+        <v>78769</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,13 +3376,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494908</v>
+        <v>494727</v>
       </c>
       <c r="R28" t="n">
-        <v>6847305</v>
+        <v>6847673</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3426,12 +3426,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123403597</v>
+        <v>123403076</v>
       </c>
       <c r="B2" t="n">
-        <v>78414</v>
+        <v>79881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494804</v>
+        <v>494829</v>
       </c>
       <c r="R2" t="n">
-        <v>6847196</v>
+        <v>6847079</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123395906</v>
+        <v>123402474</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>90957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494732</v>
+        <v>494859</v>
       </c>
       <c r="R3" t="n">
-        <v>6847579</v>
+        <v>6847114</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123396228</v>
+        <v>123395955</v>
       </c>
       <c r="B4" t="n">
-        <v>79358</v>
+        <v>78508</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494766</v>
+        <v>494764</v>
       </c>
       <c r="R4" t="n">
-        <v>6847564</v>
+        <v>6847568</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123397886</v>
+        <v>123396986</v>
       </c>
       <c r="B5" t="n">
-        <v>79851</v>
+        <v>78508</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494832</v>
+        <v>494778</v>
       </c>
       <c r="R5" t="n">
-        <v>6847342</v>
+        <v>6847448</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123396986</v>
+        <v>123399650</v>
       </c>
       <c r="B6" t="n">
-        <v>78506</v>
+        <v>79881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494778</v>
+        <v>494916</v>
       </c>
       <c r="R6" t="n">
-        <v>6847448</v>
+        <v>6847423</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123399373</v>
+        <v>123395906</v>
       </c>
       <c r="B7" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,17 +1221,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494944</v>
+        <v>494732</v>
       </c>
       <c r="R7" t="n">
-        <v>6847470</v>
+        <v>6847579</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123398345</v>
+        <v>123396228</v>
       </c>
       <c r="B8" t="n">
-        <v>78769</v>
+        <v>79360</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,37 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494856</v>
+        <v>494766</v>
       </c>
       <c r="R8" t="n">
-        <v>6847291</v>
+        <v>6847564</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123397955</v>
+        <v>123402561</v>
       </c>
       <c r="B9" t="n">
-        <v>78506</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,41 +1401,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494834</v>
+        <v>494857</v>
       </c>
       <c r="R9" t="n">
-        <v>6847337</v>
+        <v>6847085</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123399860</v>
+        <v>123398723</v>
       </c>
       <c r="B10" t="n">
-        <v>78769</v>
+        <v>78507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494841</v>
+        <v>494908</v>
       </c>
       <c r="R10" t="n">
-        <v>6847322</v>
+        <v>6847305</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,22 +1581,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123399650</v>
+        <v>123402845</v>
       </c>
       <c r="B11" t="n">
-        <v>79879</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,38 +1605,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494916</v>
+        <v>494845</v>
       </c>
       <c r="R11" t="n">
-        <v>6847423</v>
+        <v>6847104</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,22 +1692,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123398955</v>
+        <v>123402463</v>
       </c>
       <c r="B12" t="n">
-        <v>78505</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494898</v>
+        <v>494846</v>
       </c>
       <c r="R12" t="n">
-        <v>6847337</v>
+        <v>6847218</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1797,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123398038</v>
+        <v>123395505</v>
       </c>
       <c r="B13" t="n">
-        <v>78769</v>
+        <v>78508</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494836</v>
+        <v>494727</v>
       </c>
       <c r="R13" t="n">
-        <v>6847308</v>
+        <v>6847677</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1899,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123403076</v>
+        <v>123397886</v>
       </c>
       <c r="B14" t="n">
-        <v>79879</v>
+        <v>79853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1920,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494829</v>
+        <v>494832</v>
       </c>
       <c r="R14" t="n">
-        <v>6847079</v>
+        <v>6847342</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2001,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123395955</v>
+        <v>123397848</v>
       </c>
       <c r="B15" t="n">
-        <v>78506</v>
+        <v>78416</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494764</v>
+        <v>494825</v>
       </c>
       <c r="R15" t="n">
-        <v>6847568</v>
+        <v>6847351</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2103,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123395990</v>
+        <v>123399373</v>
       </c>
       <c r="B16" t="n">
-        <v>78505</v>
+        <v>78771</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,37 +2128,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494764</v>
+        <v>494944</v>
       </c>
       <c r="R16" t="n">
-        <v>6847568</v>
+        <v>6847470</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2193,22 +2202,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123398723</v>
+        <v>123396886</v>
       </c>
       <c r="B17" t="n">
-        <v>78505</v>
+        <v>78416</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,13 +2254,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494908</v>
+        <v>494774</v>
       </c>
       <c r="R17" t="n">
-        <v>6847305</v>
+        <v>6847453</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2307,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123395505</v>
+        <v>123402870</v>
       </c>
       <c r="B18" t="n">
-        <v>78506</v>
+        <v>98370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2328,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,13 +2356,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494727</v>
+        <v>494829</v>
       </c>
       <c r="R18" t="n">
-        <v>6847677</v>
+        <v>6847079</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2409,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123402845</v>
+        <v>123398955</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>78507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,50 +2430,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494845</v>
+        <v>494898</v>
       </c>
       <c r="R19" t="n">
-        <v>6847104</v>
+        <v>6847337</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2508,22 +2508,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123402561</v>
+        <v>123395990</v>
       </c>
       <c r="B20" t="n">
-        <v>98368</v>
+        <v>78507</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,25 +2532,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494857</v>
+        <v>494764</v>
       </c>
       <c r="R20" t="n">
-        <v>6847085</v>
+        <v>6847568</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123402870</v>
+        <v>123398134</v>
       </c>
       <c r="B21" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,25 +2634,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,13 +2662,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494829</v>
+        <v>494855</v>
       </c>
       <c r="R21" t="n">
-        <v>6847079</v>
+        <v>6847271</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123398134</v>
+        <v>123397955</v>
       </c>
       <c r="B22" t="n">
-        <v>78769</v>
+        <v>78508</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,37 +2740,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494855</v>
+        <v>494834</v>
       </c>
       <c r="R22" t="n">
-        <v>6847271</v>
+        <v>6847337</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2814,22 +2814,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123398359</v>
+        <v>123403597</v>
       </c>
       <c r="B23" t="n">
-        <v>78769</v>
+        <v>78416</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494882</v>
+        <v>494804</v>
       </c>
       <c r="R23" t="n">
-        <v>6847247</v>
+        <v>6847196</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123396886</v>
+        <v>123398345</v>
       </c>
       <c r="B24" t="n">
-        <v>78414</v>
+        <v>78771</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2944,37 +2944,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494774</v>
+        <v>494856</v>
       </c>
       <c r="R24" t="n">
-        <v>6847453</v>
+        <v>6847291</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3018,22 +3018,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123402463</v>
+        <v>123398359</v>
       </c>
       <c r="B25" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,25 +3042,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494846</v>
+        <v>494882</v>
       </c>
       <c r="R25" t="n">
-        <v>6847218</v>
+        <v>6847247</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123397848</v>
+        <v>123399860</v>
       </c>
       <c r="B26" t="n">
-        <v>78414</v>
+        <v>78771</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3148,37 +3148,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494825</v>
+        <v>494841</v>
       </c>
       <c r="R26" t="n">
-        <v>6847351</v>
+        <v>6847322</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3222,22 +3222,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123402474</v>
+        <v>123395626</v>
       </c>
       <c r="B27" t="n">
-        <v>90955</v>
+        <v>78771</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494859</v>
+        <v>494727</v>
       </c>
       <c r="R27" t="n">
-        <v>6847114</v>
+        <v>6847673</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3324,22 +3324,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123395626</v>
+        <v>123398038</v>
       </c>
       <c r="B28" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3376,13 +3376,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494727</v>
+        <v>494836</v>
       </c>
       <c r="R28" t="n">
-        <v>6847673</v>
+        <v>6847308</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3426,12 +3426,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123403076</v>
+        <v>123399650</v>
       </c>
       <c r="B2" t="n">
-        <v>79881</v>
+        <v>79882</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494829</v>
+        <v>494916</v>
       </c>
       <c r="R2" t="n">
-        <v>6847079</v>
+        <v>6847423</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123402474</v>
+        <v>123396228</v>
       </c>
       <c r="B3" t="n">
-        <v>90957</v>
+        <v>79361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494859</v>
+        <v>494766</v>
       </c>
       <c r="R3" t="n">
-        <v>6847114</v>
+        <v>6847564</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123395955</v>
+        <v>123402561</v>
       </c>
       <c r="B4" t="n">
-        <v>78508</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494764</v>
+        <v>494857</v>
       </c>
       <c r="R4" t="n">
-        <v>6847568</v>
+        <v>6847085</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123396986</v>
+        <v>123397886</v>
       </c>
       <c r="B5" t="n">
-        <v>78508</v>
+        <v>79854</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494778</v>
+        <v>494832</v>
       </c>
       <c r="R5" t="n">
-        <v>6847448</v>
+        <v>6847342</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123399650</v>
+        <v>123398134</v>
       </c>
       <c r="B6" t="n">
-        <v>79881</v>
+        <v>78772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494916</v>
+        <v>494855</v>
       </c>
       <c r="R6" t="n">
-        <v>6847423</v>
+        <v>6847271</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123395906</v>
+        <v>123396886</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>78417</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494732</v>
+        <v>494774</v>
       </c>
       <c r="R7" t="n">
-        <v>6847579</v>
+        <v>6847453</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123396228</v>
+        <v>123398955</v>
       </c>
       <c r="B8" t="n">
-        <v>79360</v>
+        <v>78508</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494766</v>
+        <v>494898</v>
       </c>
       <c r="R8" t="n">
-        <v>6847564</v>
+        <v>6847337</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123402561</v>
+        <v>123399860</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,41 +1401,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494857</v>
+        <v>494841</v>
       </c>
       <c r="R9" t="n">
-        <v>6847085</v>
+        <v>6847322</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123398723</v>
+        <v>123398359</v>
       </c>
       <c r="B10" t="n">
-        <v>78507</v>
+        <v>78772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494908</v>
+        <v>494882</v>
       </c>
       <c r="R10" t="n">
-        <v>6847305</v>
+        <v>6847247</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123402845</v>
+        <v>123403597</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>78417</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,50 +1605,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494845</v>
+        <v>494804</v>
       </c>
       <c r="R11" t="n">
-        <v>6847104</v>
+        <v>6847196</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1692,22 +1683,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123402463</v>
+        <v>123397955</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>78509</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,41 +1707,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494846</v>
+        <v>494834</v>
       </c>
       <c r="R12" t="n">
-        <v>6847218</v>
+        <v>6847337</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,22 +1785,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123395505</v>
+        <v>123395955</v>
       </c>
       <c r="B13" t="n">
-        <v>78508</v>
+        <v>78509</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1846,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494727</v>
+        <v>494764</v>
       </c>
       <c r="R13" t="n">
-        <v>6847677</v>
+        <v>6847568</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1908,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123397886</v>
+        <v>123398723</v>
       </c>
       <c r="B14" t="n">
-        <v>79853</v>
+        <v>78508</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494832</v>
+        <v>494908</v>
       </c>
       <c r="R14" t="n">
-        <v>6847342</v>
+        <v>6847305</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2010,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123397848</v>
+        <v>123399373</v>
       </c>
       <c r="B15" t="n">
-        <v>78416</v>
+        <v>78772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,37 +2017,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494825</v>
+        <v>494944</v>
       </c>
       <c r="R15" t="n">
-        <v>6847351</v>
+        <v>6847470</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2100,22 +2091,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123399373</v>
+        <v>123395626</v>
       </c>
       <c r="B16" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,14 +2139,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494944</v>
+        <v>494727</v>
       </c>
       <c r="R16" t="n">
-        <v>6847470</v>
+        <v>6847673</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123396886</v>
+        <v>123402463</v>
       </c>
       <c r="B17" t="n">
-        <v>78416</v>
+        <v>98376</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,13 +2245,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494774</v>
+        <v>494846</v>
       </c>
       <c r="R17" t="n">
-        <v>6847453</v>
+        <v>6847218</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2316,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123402870</v>
+        <v>123397848</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>78417</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,13 +2347,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494829</v>
+        <v>494825</v>
       </c>
       <c r="R18" t="n">
-        <v>6847079</v>
+        <v>6847351</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2418,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123398955</v>
+        <v>123402845</v>
       </c>
       <c r="B19" t="n">
-        <v>78507</v>
+        <v>98376</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,41 +2421,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494898</v>
+        <v>494845</v>
       </c>
       <c r="R19" t="n">
-        <v>6847337</v>
+        <v>6847104</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2508,22 +2508,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123395990</v>
+        <v>123402474</v>
       </c>
       <c r="B20" t="n">
-        <v>78507</v>
+        <v>90963</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494764</v>
+        <v>494859</v>
       </c>
       <c r="R20" t="n">
-        <v>6847568</v>
+        <v>6847114</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123398134</v>
+        <v>123403076</v>
       </c>
       <c r="B21" t="n">
-        <v>78771</v>
+        <v>79882</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,25 +2634,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494855</v>
+        <v>494829</v>
       </c>
       <c r="R21" t="n">
-        <v>6847271</v>
+        <v>6847079</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123397955</v>
+        <v>123402870</v>
       </c>
       <c r="B22" t="n">
-        <v>78508</v>
+        <v>98376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,41 +2736,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494834</v>
+        <v>494829</v>
       </c>
       <c r="R22" t="n">
-        <v>6847337</v>
+        <v>6847079</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2814,22 +2814,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123403597</v>
+        <v>123395906</v>
       </c>
       <c r="B23" t="n">
-        <v>78416</v>
+        <v>78772</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,13 +2866,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494804</v>
+        <v>494732</v>
       </c>
       <c r="R23" t="n">
-        <v>6847196</v>
+        <v>6847579</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2916,22 +2916,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123398345</v>
+        <v>123396986</v>
       </c>
       <c r="B24" t="n">
-        <v>78771</v>
+        <v>78509</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2944,37 +2944,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494856</v>
+        <v>494778</v>
       </c>
       <c r="R24" t="n">
-        <v>6847291</v>
+        <v>6847448</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3018,22 +3018,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123398359</v>
+        <v>123395505</v>
       </c>
       <c r="B25" t="n">
-        <v>78771</v>
+        <v>78509</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494882</v>
+        <v>494727</v>
       </c>
       <c r="R25" t="n">
-        <v>6847247</v>
+        <v>6847677</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123399860</v>
+        <v>123395990</v>
       </c>
       <c r="B26" t="n">
-        <v>78771</v>
+        <v>78508</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3148,37 +3148,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494841</v>
+        <v>494764</v>
       </c>
       <c r="R26" t="n">
-        <v>6847322</v>
+        <v>6847568</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3222,22 +3222,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123395626</v>
+        <v>123398345</v>
       </c>
       <c r="B27" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3270,17 +3270,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494727</v>
+        <v>494856</v>
       </c>
       <c r="R27" t="n">
-        <v>6847673</v>
+        <v>6847291</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>123398038</v>
       </c>
       <c r="B28" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123399650</v>
+        <v>123402463</v>
       </c>
       <c r="B2" t="n">
-        <v>79882</v>
+        <v>98379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494916</v>
+        <v>494846</v>
       </c>
       <c r="R2" t="n">
-        <v>6847423</v>
+        <v>6847218</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123396228</v>
+        <v>123396886</v>
       </c>
       <c r="B3" t="n">
-        <v>79361</v>
+        <v>78420</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494766</v>
+        <v>494774</v>
       </c>
       <c r="R3" t="n">
-        <v>6847564</v>
+        <v>6847453</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123402561</v>
+        <v>123395626</v>
       </c>
       <c r="B4" t="n">
-        <v>98376</v>
+        <v>78775</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494857</v>
+        <v>494727</v>
       </c>
       <c r="R4" t="n">
-        <v>6847085</v>
+        <v>6847673</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123397886</v>
+        <v>123403076</v>
       </c>
       <c r="B5" t="n">
-        <v>79854</v>
+        <v>79885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494832</v>
+        <v>494829</v>
       </c>
       <c r="R5" t="n">
-        <v>6847342</v>
+        <v>6847079</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123398134</v>
+        <v>123398038</v>
       </c>
       <c r="B6" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494855</v>
+        <v>494836</v>
       </c>
       <c r="R6" t="n">
-        <v>6847271</v>
+        <v>6847308</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123396886</v>
+        <v>123399650</v>
       </c>
       <c r="B7" t="n">
-        <v>78417</v>
+        <v>79885</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494774</v>
+        <v>494916</v>
       </c>
       <c r="R7" t="n">
-        <v>6847453</v>
+        <v>6847423</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123398955</v>
+        <v>123402474</v>
       </c>
       <c r="B8" t="n">
-        <v>78508</v>
+        <v>90966</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494898</v>
+        <v>494859</v>
       </c>
       <c r="R8" t="n">
-        <v>6847337</v>
+        <v>6847114</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123399860</v>
+        <v>123402845</v>
       </c>
       <c r="B9" t="n">
-        <v>78772</v>
+        <v>98379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,41 +1401,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494841</v>
+        <v>494845</v>
       </c>
       <c r="R9" t="n">
-        <v>6847322</v>
+        <v>6847104</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1503,7 @@
         <v>123398359</v>
       </c>
       <c r="B10" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123403597</v>
+        <v>123399373</v>
       </c>
       <c r="B11" t="n">
-        <v>78417</v>
+        <v>78775</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,37 +1618,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494804</v>
+        <v>494944</v>
       </c>
       <c r="R11" t="n">
-        <v>6847196</v>
+        <v>6847470</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1683,22 +1692,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123397955</v>
+        <v>123396228</v>
       </c>
       <c r="B12" t="n">
-        <v>78509</v>
+        <v>79364</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,37 +1720,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494834</v>
+        <v>494766</v>
       </c>
       <c r="R12" t="n">
-        <v>6847337</v>
+        <v>6847564</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,22 +1794,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123395955</v>
+        <v>123397848</v>
       </c>
       <c r="B13" t="n">
-        <v>78509</v>
+        <v>78420</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494764</v>
+        <v>494825</v>
       </c>
       <c r="R13" t="n">
-        <v>6847568</v>
+        <v>6847351</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1899,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123398723</v>
+        <v>123398345</v>
       </c>
       <c r="B14" t="n">
-        <v>78508</v>
+        <v>78775</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,37 +1924,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494908</v>
+        <v>494856</v>
       </c>
       <c r="R14" t="n">
-        <v>6847305</v>
+        <v>6847291</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1989,22 +1998,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123399373</v>
+        <v>123397955</v>
       </c>
       <c r="B15" t="n">
-        <v>78772</v>
+        <v>78512</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,13 +2050,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494944</v>
+        <v>494834</v>
       </c>
       <c r="R15" t="n">
-        <v>6847470</v>
+        <v>6847337</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2103,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123395626</v>
+        <v>123395505</v>
       </c>
       <c r="B16" t="n">
-        <v>78772</v>
+        <v>78512</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2146,10 +2155,10 @@
         <v>494727</v>
       </c>
       <c r="R16" t="n">
-        <v>6847673</v>
+        <v>6847677</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2193,22 +2202,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123402463</v>
+        <v>123399860</v>
       </c>
       <c r="B17" t="n">
-        <v>98376</v>
+        <v>78775</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,41 +2226,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494846</v>
+        <v>494841</v>
       </c>
       <c r="R17" t="n">
-        <v>6847218</v>
+        <v>6847322</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2295,22 +2304,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123397848</v>
+        <v>123395906</v>
       </c>
       <c r="B18" t="n">
-        <v>78417</v>
+        <v>78775</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,13 +2356,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494825</v>
+        <v>494732</v>
       </c>
       <c r="R18" t="n">
-        <v>6847351</v>
+        <v>6847579</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2397,22 +2406,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123402845</v>
+        <v>123402561</v>
       </c>
       <c r="B19" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2442,26 +2451,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494845</v>
+        <v>494857</v>
       </c>
       <c r="R19" t="n">
-        <v>6847104</v>
+        <v>6847085</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,22 +2508,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123402474</v>
+        <v>123402870</v>
       </c>
       <c r="B20" t="n">
-        <v>90963</v>
+        <v>98379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,25 +2532,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494859</v>
+        <v>494829</v>
       </c>
       <c r="R20" t="n">
-        <v>6847114</v>
+        <v>6847079</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123403076</v>
+        <v>123398723</v>
       </c>
       <c r="B21" t="n">
-        <v>79882</v>
+        <v>78511</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,25 +2634,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494829</v>
+        <v>494908</v>
       </c>
       <c r="R21" t="n">
-        <v>6847079</v>
+        <v>6847305</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123402870</v>
+        <v>123403597</v>
       </c>
       <c r="B22" t="n">
-        <v>98376</v>
+        <v>78420</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,13 +2764,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494829</v>
+        <v>494804</v>
       </c>
       <c r="R22" t="n">
-        <v>6847079</v>
+        <v>6847196</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123395906</v>
+        <v>123397886</v>
       </c>
       <c r="B23" t="n">
-        <v>78772</v>
+        <v>79857</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,13 +2866,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494732</v>
+        <v>494832</v>
       </c>
       <c r="R23" t="n">
-        <v>6847579</v>
+        <v>6847342</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2916,22 +2916,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123396986</v>
+        <v>123395990</v>
       </c>
       <c r="B24" t="n">
-        <v>78509</v>
+        <v>78511</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2944,21 +2944,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494778</v>
+        <v>494764</v>
       </c>
       <c r="R24" t="n">
-        <v>6847448</v>
+        <v>6847568</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123395505</v>
+        <v>123395955</v>
       </c>
       <c r="B25" t="n">
-        <v>78509</v>
+        <v>78512</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494727</v>
+        <v>494764</v>
       </c>
       <c r="R25" t="n">
-        <v>6847677</v>
+        <v>6847568</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123395990</v>
+        <v>123396986</v>
       </c>
       <c r="B26" t="n">
-        <v>78508</v>
+        <v>78512</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3148,21 +3148,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494764</v>
+        <v>494778</v>
       </c>
       <c r="R26" t="n">
-        <v>6847568</v>
+        <v>6847448</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123398345</v>
+        <v>123398134</v>
       </c>
       <c r="B27" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3270,17 +3270,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494856</v>
+        <v>494855</v>
       </c>
       <c r="R27" t="n">
-        <v>6847291</v>
+        <v>6847271</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3324,22 +3324,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123398038</v>
+        <v>123398955</v>
       </c>
       <c r="B28" t="n">
-        <v>78772</v>
+        <v>78511</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494836</v>
+        <v>494898</v>
       </c>
       <c r="R28" t="n">
-        <v>6847308</v>
+        <v>6847337</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123402463</v>
+        <v>123397955</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>78518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494846</v>
+        <v>494834</v>
       </c>
       <c r="R2" t="n">
-        <v>6847218</v>
+        <v>6847337</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123396886</v>
+        <v>123399373</v>
       </c>
       <c r="B3" t="n">
-        <v>78420</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494774</v>
+        <v>494944</v>
       </c>
       <c r="R3" t="n">
-        <v>6847453</v>
+        <v>6847470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,7 +882,7 @@
         <v>123395626</v>
       </c>
       <c r="B4" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123403076</v>
+        <v>123398134</v>
       </c>
       <c r="B5" t="n">
-        <v>79885</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494829</v>
+        <v>494855</v>
       </c>
       <c r="R5" t="n">
-        <v>6847079</v>
+        <v>6847271</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123398038</v>
+        <v>123402845</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1095,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494836</v>
+        <v>494845</v>
       </c>
       <c r="R6" t="n">
-        <v>6847308</v>
+        <v>6847104</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,22 +1182,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123399650</v>
+        <v>123396228</v>
       </c>
       <c r="B7" t="n">
-        <v>79885</v>
+        <v>79370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494916</v>
+        <v>494766</v>
       </c>
       <c r="R7" t="n">
-        <v>6847423</v>
+        <v>6847564</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1299,7 @@
         <v>123402474</v>
       </c>
       <c r="B8" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123402845</v>
+        <v>123402561</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1422,26 +1431,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494845</v>
+        <v>494857</v>
       </c>
       <c r="R9" t="n">
-        <v>6847104</v>
+        <v>6847085</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,22 +1488,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123398359</v>
+        <v>123399650</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,13 +1540,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494882</v>
+        <v>494916</v>
       </c>
       <c r="R10" t="n">
-        <v>6847247</v>
+        <v>6847423</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123399373</v>
+        <v>123396986</v>
       </c>
       <c r="B11" t="n">
-        <v>78775</v>
+        <v>78518</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,37 +1618,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494944</v>
+        <v>494778</v>
       </c>
       <c r="R11" t="n">
-        <v>6847470</v>
+        <v>6847448</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1692,22 +1692,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123396228</v>
+        <v>123397848</v>
       </c>
       <c r="B12" t="n">
-        <v>79364</v>
+        <v>78426</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,13 +1744,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494766</v>
+        <v>494825</v>
       </c>
       <c r="R12" t="n">
-        <v>6847564</v>
+        <v>6847351</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123397848</v>
+        <v>123403076</v>
       </c>
       <c r="B13" t="n">
-        <v>78420</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494825</v>
+        <v>494829</v>
       </c>
       <c r="R13" t="n">
-        <v>6847351</v>
+        <v>6847079</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123398345</v>
+        <v>123395906</v>
       </c>
       <c r="B14" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,14 +1944,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494856</v>
+        <v>494732</v>
       </c>
       <c r="R14" t="n">
-        <v>6847291</v>
+        <v>6847579</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123397955</v>
+        <v>123402870</v>
       </c>
       <c r="B15" t="n">
-        <v>78512</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,41 +2022,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494834</v>
+        <v>494829</v>
       </c>
       <c r="R15" t="n">
-        <v>6847337</v>
+        <v>6847079</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2100,22 +2100,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123395505</v>
+        <v>123398723</v>
       </c>
       <c r="B16" t="n">
-        <v>78512</v>
+        <v>78517</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494727</v>
+        <v>494908</v>
       </c>
       <c r="R16" t="n">
-        <v>6847677</v>
+        <v>6847305</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123399860</v>
+        <v>123395990</v>
       </c>
       <c r="B17" t="n">
-        <v>78775</v>
+        <v>78517</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,37 +2230,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494841</v>
+        <v>494764</v>
       </c>
       <c r="R17" t="n">
-        <v>6847322</v>
+        <v>6847568</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2304,22 +2304,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123395906</v>
+        <v>123398345</v>
       </c>
       <c r="B18" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,14 +2352,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494732</v>
+        <v>494856</v>
       </c>
       <c r="R18" t="n">
-        <v>6847579</v>
+        <v>6847291</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123402561</v>
+        <v>123398955</v>
       </c>
       <c r="B19" t="n">
-        <v>98379</v>
+        <v>78517</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,25 +2430,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494857</v>
+        <v>494898</v>
       </c>
       <c r="R19" t="n">
-        <v>6847085</v>
+        <v>6847337</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123402870</v>
+        <v>123396886</v>
       </c>
       <c r="B20" t="n">
-        <v>98379</v>
+        <v>78426</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,25 +2532,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494829</v>
+        <v>494774</v>
       </c>
       <c r="R20" t="n">
-        <v>6847079</v>
+        <v>6847453</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123398723</v>
+        <v>123395955</v>
       </c>
       <c r="B21" t="n">
-        <v>78511</v>
+        <v>78518</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2638,21 +2638,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494908</v>
+        <v>494764</v>
       </c>
       <c r="R21" t="n">
-        <v>6847305</v>
+        <v>6847568</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123403597</v>
+        <v>123397886</v>
       </c>
       <c r="B22" t="n">
-        <v>78420</v>
+        <v>79863</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494804</v>
+        <v>494832</v>
       </c>
       <c r="R22" t="n">
-        <v>6847196</v>
+        <v>6847342</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123397886</v>
+        <v>123398359</v>
       </c>
       <c r="B23" t="n">
-        <v>79857</v>
+        <v>78781</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494832</v>
+        <v>494882</v>
       </c>
       <c r="R23" t="n">
-        <v>6847342</v>
+        <v>6847247</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123395990</v>
+        <v>123399860</v>
       </c>
       <c r="B24" t="n">
-        <v>78511</v>
+        <v>78781</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2944,37 +2944,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494764</v>
+        <v>494841</v>
       </c>
       <c r="R24" t="n">
-        <v>6847568</v>
+        <v>6847322</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3018,22 +3018,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123395955</v>
+        <v>123402463</v>
       </c>
       <c r="B25" t="n">
-        <v>78512</v>
+        <v>98396</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,25 +3042,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494764</v>
+        <v>494846</v>
       </c>
       <c r="R25" t="n">
-        <v>6847568</v>
+        <v>6847218</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123396986</v>
+        <v>123398038</v>
       </c>
       <c r="B26" t="n">
-        <v>78512</v>
+        <v>78781</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3148,21 +3148,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494778</v>
+        <v>494836</v>
       </c>
       <c r="R26" t="n">
-        <v>6847448</v>
+        <v>6847308</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123398134</v>
+        <v>123395505</v>
       </c>
       <c r="B27" t="n">
-        <v>78775</v>
+        <v>78518</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494855</v>
+        <v>494727</v>
       </c>
       <c r="R27" t="n">
-        <v>6847271</v>
+        <v>6847677</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123398955</v>
+        <v>123403597</v>
       </c>
       <c r="B28" t="n">
-        <v>78511</v>
+        <v>78426</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494898</v>
+        <v>494804</v>
       </c>
       <c r="R28" t="n">
-        <v>6847337</v>
+        <v>6847196</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123396228</v>
+        <v>123402561</v>
       </c>
       <c r="B7" t="n">
-        <v>79370</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494766</v>
+        <v>494857</v>
       </c>
       <c r="R7" t="n">
-        <v>6847564</v>
+        <v>6847085</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123402474</v>
+        <v>123396228</v>
       </c>
       <c r="B8" t="n">
-        <v>90983</v>
+        <v>79370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494859</v>
+        <v>494766</v>
       </c>
       <c r="R8" t="n">
-        <v>6847114</v>
+        <v>6847564</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123402561</v>
+        <v>123402474</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>90983</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494857</v>
+        <v>494859</v>
       </c>
       <c r="R9" t="n">
-        <v>6847085</v>
+        <v>6847114</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123395990</v>
+        <v>123396886</v>
       </c>
       <c r="B17" t="n">
-        <v>78517</v>
+        <v>78426</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,13 +2254,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494764</v>
+        <v>494774</v>
       </c>
       <c r="R17" t="n">
-        <v>6847568</v>
+        <v>6847453</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123398345</v>
+        <v>123395990</v>
       </c>
       <c r="B18" t="n">
-        <v>78781</v>
+        <v>78517</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,37 +2332,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494856</v>
+        <v>494764</v>
       </c>
       <c r="R18" t="n">
-        <v>6847291</v>
+        <v>6847568</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2406,22 +2406,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123398955</v>
+        <v>123398345</v>
       </c>
       <c r="B19" t="n">
-        <v>78517</v>
+        <v>78781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,37 +2434,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494898</v>
+        <v>494856</v>
       </c>
       <c r="R19" t="n">
-        <v>6847337</v>
+        <v>6847291</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2508,22 +2508,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123396886</v>
+        <v>123398955</v>
       </c>
       <c r="B20" t="n">
-        <v>78426</v>
+        <v>78517</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494774</v>
+        <v>494898</v>
       </c>
       <c r="R20" t="n">
-        <v>6847453</v>
+        <v>6847337</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123399860</v>
+        <v>123402463</v>
       </c>
       <c r="B24" t="n">
-        <v>78781</v>
+        <v>98396</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,41 +2940,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494841</v>
+        <v>494846</v>
       </c>
       <c r="R24" t="n">
-        <v>6847322</v>
+        <v>6847218</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3018,22 +3018,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123402463</v>
+        <v>123399860</v>
       </c>
       <c r="B25" t="n">
-        <v>98396</v>
+        <v>78781</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,41 +3042,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494846</v>
+        <v>494841</v>
       </c>
       <c r="R25" t="n">
-        <v>6847218</v>
+        <v>6847322</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3120,12 +3120,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123402561</v>
+        <v>123396228</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>79370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494857</v>
+        <v>494766</v>
       </c>
       <c r="R7" t="n">
-        <v>6847085</v>
+        <v>6847564</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123396228</v>
+        <v>123402474</v>
       </c>
       <c r="B8" t="n">
-        <v>79370</v>
+        <v>90983</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494766</v>
+        <v>494859</v>
       </c>
       <c r="R8" t="n">
-        <v>6847564</v>
+        <v>6847114</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123402474</v>
+        <v>123402561</v>
       </c>
       <c r="B9" t="n">
-        <v>90983</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494859</v>
+        <v>494857</v>
       </c>
       <c r="R9" t="n">
-        <v>6847114</v>
+        <v>6847085</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123402463</v>
+        <v>123399860</v>
       </c>
       <c r="B24" t="n">
-        <v>98396</v>
+        <v>78781</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,41 +2940,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494846</v>
+        <v>494841</v>
       </c>
       <c r="R24" t="n">
-        <v>6847218</v>
+        <v>6847322</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3018,22 +3018,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123399860</v>
+        <v>123402463</v>
       </c>
       <c r="B25" t="n">
-        <v>78781</v>
+        <v>98396</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,41 +3042,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494841</v>
+        <v>494846</v>
       </c>
       <c r="R25" t="n">
-        <v>6847322</v>
+        <v>6847218</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3120,12 +3120,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123396886</v>
+        <v>123395990</v>
       </c>
       <c r="B17" t="n">
-        <v>78426</v>
+        <v>78517</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,13 +2254,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494774</v>
+        <v>494764</v>
       </c>
       <c r="R17" t="n">
-        <v>6847453</v>
+        <v>6847568</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123395990</v>
+        <v>123398345</v>
       </c>
       <c r="B18" t="n">
-        <v>78517</v>
+        <v>78781</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,37 +2332,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494764</v>
+        <v>494856</v>
       </c>
       <c r="R18" t="n">
-        <v>6847568</v>
+        <v>6847291</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2406,22 +2406,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123398345</v>
+        <v>123398955</v>
       </c>
       <c r="B19" t="n">
-        <v>78781</v>
+        <v>78517</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,37 +2434,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494856</v>
+        <v>494898</v>
       </c>
       <c r="R19" t="n">
-        <v>6847291</v>
+        <v>6847337</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2508,22 +2508,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123398955</v>
+        <v>123396886</v>
       </c>
       <c r="B20" t="n">
-        <v>78517</v>
+        <v>78426</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494898</v>
+        <v>494774</v>
       </c>
       <c r="R20" t="n">
-        <v>6847337</v>
+        <v>6847453</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123395955</v>
+        <v>123397886</v>
       </c>
       <c r="B21" t="n">
-        <v>78518</v>
+        <v>79863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2638,21 +2638,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494764</v>
+        <v>494832</v>
       </c>
       <c r="R21" t="n">
-        <v>6847568</v>
+        <v>6847342</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123397886</v>
+        <v>123395955</v>
       </c>
       <c r="B22" t="n">
-        <v>79863</v>
+        <v>78518</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494832</v>
+        <v>494764</v>
       </c>
       <c r="R22" t="n">
-        <v>6847342</v>
+        <v>6847568</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123397955</v>
+        <v>123402561</v>
       </c>
       <c r="B2" t="n">
-        <v>78518</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494834</v>
+        <v>494857</v>
       </c>
       <c r="R2" t="n">
-        <v>6847337</v>
+        <v>6847085</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123399373</v>
+        <v>123395955</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>78523</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494944</v>
+        <v>494764</v>
       </c>
       <c r="R3" t="n">
-        <v>6847470</v>
+        <v>6847568</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123395626</v>
+        <v>123398359</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494727</v>
+        <v>494882</v>
       </c>
       <c r="R4" t="n">
-        <v>6847673</v>
+        <v>6847247</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123398134</v>
+        <v>123402845</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +993,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494855</v>
+        <v>494845</v>
       </c>
       <c r="R5" t="n">
-        <v>6847271</v>
+        <v>6847104</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1080,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123402845</v>
+        <v>123403597</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>78431</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,50 +1104,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494845</v>
+        <v>494804</v>
       </c>
       <c r="R6" t="n">
-        <v>6847104</v>
+        <v>6847196</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,22 +1182,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123396228</v>
+        <v>123403076</v>
       </c>
       <c r="B7" t="n">
-        <v>79370</v>
+        <v>79896</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,13 +1234,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494766</v>
+        <v>494829</v>
       </c>
       <c r="R7" t="n">
-        <v>6847564</v>
+        <v>6847079</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123402474</v>
+        <v>123398723</v>
       </c>
       <c r="B8" t="n">
-        <v>90983</v>
+        <v>78522</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494859</v>
+        <v>494908</v>
       </c>
       <c r="R8" t="n">
-        <v>6847114</v>
+        <v>6847305</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123402561</v>
+        <v>123395906</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>78786</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494857</v>
+        <v>494732</v>
       </c>
       <c r="R9" t="n">
-        <v>6847085</v>
+        <v>6847579</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1488,22 +1488,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123399650</v>
+        <v>123395505</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>78523</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,13 +1540,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494916</v>
+        <v>494727</v>
       </c>
       <c r="R10" t="n">
-        <v>6847423</v>
+        <v>6847677</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123396986</v>
+        <v>123396886</v>
       </c>
       <c r="B11" t="n">
-        <v>78518</v>
+        <v>78431</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,13 +1642,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494778</v>
+        <v>494774</v>
       </c>
       <c r="R11" t="n">
-        <v>6847448</v>
+        <v>6847453</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123397848</v>
+        <v>123402870</v>
       </c>
       <c r="B12" t="n">
-        <v>78426</v>
+        <v>98502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,13 +1744,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494825</v>
+        <v>494829</v>
       </c>
       <c r="R12" t="n">
-        <v>6847351</v>
+        <v>6847079</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123403076</v>
+        <v>123398134</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>78786</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494829</v>
+        <v>494855</v>
       </c>
       <c r="R13" t="n">
-        <v>6847079</v>
+        <v>6847271</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123395906</v>
+        <v>123402463</v>
       </c>
       <c r="B14" t="n">
-        <v>78781</v>
+        <v>98502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,25 +1920,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494732</v>
+        <v>494846</v>
       </c>
       <c r="R14" t="n">
-        <v>6847579</v>
+        <v>6847218</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1998,22 +1998,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123402870</v>
+        <v>123402474</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>90988</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,25 +2022,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494829</v>
+        <v>494859</v>
       </c>
       <c r="R15" t="n">
-        <v>6847079</v>
+        <v>6847114</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123398723</v>
+        <v>123398038</v>
       </c>
       <c r="B16" t="n">
-        <v>78517</v>
+        <v>78786</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494908</v>
+        <v>494836</v>
       </c>
       <c r="R16" t="n">
-        <v>6847305</v>
+        <v>6847308</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2217,7 +2217,7 @@
         <v>123395990</v>
       </c>
       <c r="B17" t="n">
-        <v>78517</v>
+        <v>78522</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123398345</v>
+        <v>123395626</v>
       </c>
       <c r="B18" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,17 +2352,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494856</v>
+        <v>494727</v>
       </c>
       <c r="R18" t="n">
-        <v>6847291</v>
+        <v>6847673</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>123398955</v>
       </c>
       <c r="B19" t="n">
-        <v>78517</v>
+        <v>78522</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123396886</v>
+        <v>123396986</v>
       </c>
       <c r="B20" t="n">
-        <v>78426</v>
+        <v>78523</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494774</v>
+        <v>494778</v>
       </c>
       <c r="R20" t="n">
-        <v>6847453</v>
+        <v>6847448</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>123397886</v>
       </c>
       <c r="B21" t="n">
-        <v>79863</v>
+        <v>79868</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123395955</v>
+        <v>123399650</v>
       </c>
       <c r="B22" t="n">
-        <v>78518</v>
+        <v>79896</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,13 +2764,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494764</v>
+        <v>494916</v>
       </c>
       <c r="R22" t="n">
-        <v>6847568</v>
+        <v>6847423</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123398359</v>
+        <v>123399373</v>
       </c>
       <c r="B23" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,17 +2862,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494882</v>
+        <v>494944</v>
       </c>
       <c r="R23" t="n">
-        <v>6847247</v>
+        <v>6847470</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2916,22 +2916,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123399860</v>
+        <v>123398345</v>
       </c>
       <c r="B24" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494841</v>
+        <v>494856</v>
       </c>
       <c r="R24" t="n">
-        <v>6847322</v>
+        <v>6847291</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123402463</v>
+        <v>123399860</v>
       </c>
       <c r="B25" t="n">
-        <v>98396</v>
+        <v>78786</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,41 +3042,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494846</v>
+        <v>494841</v>
       </c>
       <c r="R25" t="n">
-        <v>6847218</v>
+        <v>6847322</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3120,22 +3120,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123398038</v>
+        <v>123396228</v>
       </c>
       <c r="B26" t="n">
-        <v>78781</v>
+        <v>79375</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3148,21 +3148,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494836</v>
+        <v>494766</v>
       </c>
       <c r="R26" t="n">
-        <v>6847308</v>
+        <v>6847564</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123395505</v>
+        <v>123397848</v>
       </c>
       <c r="B27" t="n">
-        <v>78518</v>
+        <v>78431</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494727</v>
+        <v>494825</v>
       </c>
       <c r="R27" t="n">
-        <v>6847677</v>
+        <v>6847351</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123403597</v>
+        <v>123397955</v>
       </c>
       <c r="B28" t="n">
-        <v>78426</v>
+        <v>78523</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,37 +3352,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494804</v>
+        <v>494834</v>
       </c>
       <c r="R28" t="n">
-        <v>6847196</v>
+        <v>6847337</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3426,12 +3426,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123402561</v>
+        <v>123398723</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>78524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494857</v>
+        <v>494908</v>
       </c>
       <c r="R2" t="n">
-        <v>6847085</v>
+        <v>6847305</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123395955</v>
+        <v>123402474</v>
       </c>
       <c r="B3" t="n">
-        <v>78523</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494764</v>
+        <v>494859</v>
       </c>
       <c r="R3" t="n">
-        <v>6847568</v>
+        <v>6847114</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123398359</v>
+        <v>123399373</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494882</v>
+        <v>494944</v>
       </c>
       <c r="R4" t="n">
-        <v>6847247</v>
+        <v>6847470</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123402845</v>
+        <v>123399860</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,50 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494845</v>
+        <v>494841</v>
       </c>
       <c r="R5" t="n">
-        <v>6847104</v>
+        <v>6847322</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123403597</v>
+        <v>123396886</v>
       </c>
       <c r="B6" t="n">
-        <v>78431</v>
+        <v>78433</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494804</v>
+        <v>494774</v>
       </c>
       <c r="R6" t="n">
-        <v>6847196</v>
+        <v>6847453</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,7 +1188,7 @@
         <v>123403076</v>
       </c>
       <c r="B7" t="n">
-        <v>79896</v>
+        <v>79898</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123398723</v>
+        <v>123402463</v>
       </c>
       <c r="B8" t="n">
-        <v>78522</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494908</v>
+        <v>494846</v>
       </c>
       <c r="R8" t="n">
-        <v>6847305</v>
+        <v>6847218</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1398,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123395906</v>
+        <v>123402561</v>
       </c>
       <c r="B9" t="n">
-        <v>78786</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494732</v>
+        <v>494857</v>
       </c>
       <c r="R9" t="n">
-        <v>6847579</v>
+        <v>6847085</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1488,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123395505</v>
+        <v>123395990</v>
       </c>
       <c r="B10" t="n">
-        <v>78523</v>
+        <v>78524</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494727</v>
+        <v>494764</v>
       </c>
       <c r="R10" t="n">
-        <v>6847677</v>
+        <v>6847568</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1602,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123396886</v>
+        <v>123398359</v>
       </c>
       <c r="B11" t="n">
-        <v>78431</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494774</v>
+        <v>494882</v>
       </c>
       <c r="R11" t="n">
-        <v>6847453</v>
+        <v>6847247</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123402870</v>
+        <v>123399650</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>79898</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494829</v>
+        <v>494916</v>
       </c>
       <c r="R12" t="n">
-        <v>6847079</v>
+        <v>6847423</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1809,7 +1800,7 @@
         <v>123398134</v>
       </c>
       <c r="B13" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123402463</v>
+        <v>123397886</v>
       </c>
       <c r="B14" t="n">
-        <v>98502</v>
+        <v>79870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494846</v>
+        <v>494832</v>
       </c>
       <c r="R14" t="n">
-        <v>6847218</v>
+        <v>6847342</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2010,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123402474</v>
+        <v>123398955</v>
       </c>
       <c r="B15" t="n">
-        <v>90988</v>
+        <v>78524</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,13 +2041,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494859</v>
+        <v>494898</v>
       </c>
       <c r="R15" t="n">
-        <v>6847114</v>
+        <v>6847337</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2112,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123398038</v>
+        <v>123397955</v>
       </c>
       <c r="B16" t="n">
-        <v>78786</v>
+        <v>78525</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,37 +2119,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494836</v>
+        <v>494834</v>
       </c>
       <c r="R16" t="n">
-        <v>6847308</v>
+        <v>6847337</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2202,22 +2193,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123395990</v>
+        <v>123395626</v>
       </c>
       <c r="B17" t="n">
-        <v>78522</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,13 +2245,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494764</v>
+        <v>494727</v>
       </c>
       <c r="R17" t="n">
-        <v>6847568</v>
+        <v>6847673</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2304,22 +2295,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123395626</v>
+        <v>123396228</v>
       </c>
       <c r="B18" t="n">
-        <v>78786</v>
+        <v>79377</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494727</v>
+        <v>494766</v>
       </c>
       <c r="R18" t="n">
-        <v>6847673</v>
+        <v>6847564</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2406,22 +2397,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123398955</v>
+        <v>123402845</v>
       </c>
       <c r="B19" t="n">
-        <v>78522</v>
+        <v>98504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,41 +2421,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494898</v>
+        <v>494845</v>
       </c>
       <c r="R19" t="n">
-        <v>6847337</v>
+        <v>6847104</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2508,12 +2508,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2523,7 +2523,7 @@
         <v>123396986</v>
       </c>
       <c r="B20" t="n">
-        <v>78523</v>
+        <v>78525</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123397886</v>
+        <v>123398345</v>
       </c>
       <c r="B21" t="n">
-        <v>79868</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2638,37 +2638,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494832</v>
+        <v>494856</v>
       </c>
       <c r="R21" t="n">
-        <v>6847342</v>
+        <v>6847291</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2712,22 +2712,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123399650</v>
+        <v>123398038</v>
       </c>
       <c r="B22" t="n">
-        <v>79896</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,13 +2764,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494916</v>
+        <v>494836</v>
       </c>
       <c r="R22" t="n">
-        <v>6847423</v>
+        <v>6847308</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123399373</v>
+        <v>123395505</v>
       </c>
       <c r="B23" t="n">
-        <v>78786</v>
+        <v>78525</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,37 +2842,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494944</v>
+        <v>494727</v>
       </c>
       <c r="R23" t="n">
-        <v>6847470</v>
+        <v>6847677</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2916,22 +2916,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123398345</v>
+        <v>123403597</v>
       </c>
       <c r="B24" t="n">
-        <v>78786</v>
+        <v>78433</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2944,37 +2944,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494856</v>
+        <v>494804</v>
       </c>
       <c r="R24" t="n">
-        <v>6847291</v>
+        <v>6847196</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3018,22 +3018,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123399860</v>
+        <v>123395906</v>
       </c>
       <c r="B25" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3066,14 +3066,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494841</v>
+        <v>494732</v>
       </c>
       <c r="R25" t="n">
-        <v>6847322</v>
+        <v>6847579</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123396228</v>
+        <v>123402870</v>
       </c>
       <c r="B26" t="n">
-        <v>79375</v>
+        <v>98504</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,25 +3144,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494766</v>
+        <v>494829</v>
       </c>
       <c r="R26" t="n">
-        <v>6847564</v>
+        <v>6847079</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3237,7 +3237,7 @@
         <v>123397848</v>
       </c>
       <c r="B27" t="n">
-        <v>78431</v>
+        <v>78433</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123397955</v>
+        <v>123395955</v>
       </c>
       <c r="B28" t="n">
-        <v>78523</v>
+        <v>78525</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3372,17 +3372,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494834</v>
+        <v>494764</v>
       </c>
       <c r="R28" t="n">
-        <v>6847337</v>
+        <v>6847568</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3426,12 +3426,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123398955</v>
+        <v>123397955</v>
       </c>
       <c r="B15" t="n">
-        <v>78524</v>
+        <v>78525</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,37 +2017,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494898</v>
+        <v>494834</v>
       </c>
       <c r="R15" t="n">
         <v>6847337</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2091,22 +2091,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123397955</v>
+        <v>123398955</v>
       </c>
       <c r="B16" t="n">
-        <v>78525</v>
+        <v>78524</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,37 +2119,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494834</v>
+        <v>494898</v>
       </c>
       <c r="R16" t="n">
         <v>6847337</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2193,12 +2193,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123398345</v>
+        <v>123395505</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2638,37 +2638,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494856</v>
+        <v>494727</v>
       </c>
       <c r="R21" t="n">
-        <v>6847291</v>
+        <v>6847677</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2712,19 +2712,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123398038</v>
+        <v>123398345</v>
       </c>
       <c r="B22" t="n">
         <v>78788</v>
@@ -2760,17 +2760,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494836</v>
+        <v>494856</v>
       </c>
       <c r="R22" t="n">
-        <v>6847308</v>
+        <v>6847291</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2814,22 +2814,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123395505</v>
+        <v>123398038</v>
       </c>
       <c r="B23" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494727</v>
+        <v>494836</v>
       </c>
       <c r="R23" t="n">
-        <v>6847677</v>
+        <v>6847308</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123398723</v>
+        <v>123398359</v>
       </c>
       <c r="B2" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494908</v>
+        <v>494882</v>
       </c>
       <c r="R2" t="n">
-        <v>6847305</v>
+        <v>6847247</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123402474</v>
+        <v>123395505</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>78525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494859</v>
+        <v>494727</v>
       </c>
       <c r="R3" t="n">
-        <v>6847114</v>
+        <v>6847677</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123399373</v>
+        <v>123397886</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494944</v>
+        <v>494832</v>
       </c>
       <c r="R4" t="n">
-        <v>6847470</v>
+        <v>6847342</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123399860</v>
+        <v>123397955</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494841</v>
+        <v>494834</v>
       </c>
       <c r="R5" t="n">
-        <v>6847322</v>
+        <v>6847337</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123396886</v>
+        <v>123402845</v>
       </c>
       <c r="B6" t="n">
-        <v>78433</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494774</v>
+        <v>494845</v>
       </c>
       <c r="R6" t="n">
-        <v>6847453</v>
+        <v>6847104</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,22 +1182,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123403076</v>
+        <v>123398955</v>
       </c>
       <c r="B7" t="n">
-        <v>79898</v>
+        <v>78524</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494829</v>
+        <v>494898</v>
       </c>
       <c r="R7" t="n">
-        <v>6847079</v>
+        <v>6847337</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1287,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123402463</v>
+        <v>123396228</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>79377</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1336,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494846</v>
+        <v>494766</v>
       </c>
       <c r="R8" t="n">
-        <v>6847218</v>
+        <v>6847564</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123402561</v>
+        <v>123402463</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,13 +1438,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494857</v>
+        <v>494846</v>
       </c>
       <c r="R9" t="n">
-        <v>6847085</v>
+        <v>6847218</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123395990</v>
+        <v>123398038</v>
       </c>
       <c r="B10" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494764</v>
+        <v>494836</v>
       </c>
       <c r="R10" t="n">
-        <v>6847568</v>
+        <v>6847308</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1593,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123398359</v>
+        <v>123402561</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1642,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494882</v>
+        <v>494857</v>
       </c>
       <c r="R11" t="n">
-        <v>6847247</v>
+        <v>6847085</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123399650</v>
+        <v>123398723</v>
       </c>
       <c r="B12" t="n">
-        <v>79898</v>
+        <v>78524</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,13 +1744,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494916</v>
+        <v>494908</v>
       </c>
       <c r="R12" t="n">
-        <v>6847423</v>
+        <v>6847305</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,7 +1806,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123398134</v>
+        <v>123395626</v>
       </c>
       <c r="B13" t="n">
         <v>78788</v>
@@ -1837,13 +1846,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494855</v>
+        <v>494727</v>
       </c>
       <c r="R13" t="n">
-        <v>6847271</v>
+        <v>6847673</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1887,22 +1896,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123397886</v>
+        <v>123399860</v>
       </c>
       <c r="B14" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,37 +1924,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494832</v>
+        <v>494841</v>
       </c>
       <c r="R14" t="n">
-        <v>6847342</v>
+        <v>6847322</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1989,22 +1998,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123397955</v>
+        <v>123399373</v>
       </c>
       <c r="B15" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,13 +2050,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494834</v>
+        <v>494944</v>
       </c>
       <c r="R15" t="n">
-        <v>6847337</v>
+        <v>6847470</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2103,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123398955</v>
+        <v>123395955</v>
       </c>
       <c r="B16" t="n">
-        <v>78524</v>
+        <v>78525</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494898</v>
+        <v>494764</v>
       </c>
       <c r="R16" t="n">
-        <v>6847337</v>
+        <v>6847568</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2205,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123395626</v>
+        <v>123403076</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2226,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,13 +2254,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494727</v>
+        <v>494829</v>
       </c>
       <c r="R17" t="n">
-        <v>6847673</v>
+        <v>6847079</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2295,22 +2304,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123396228</v>
+        <v>123397848</v>
       </c>
       <c r="B18" t="n">
-        <v>79377</v>
+        <v>78433</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,13 +2356,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494766</v>
+        <v>494825</v>
       </c>
       <c r="R18" t="n">
-        <v>6847564</v>
+        <v>6847351</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2409,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123402845</v>
+        <v>123402870</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2442,26 +2451,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494845</v>
+        <v>494829</v>
       </c>
       <c r="R19" t="n">
-        <v>6847104</v>
+        <v>6847079</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,22 +2508,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123396986</v>
+        <v>123398345</v>
       </c>
       <c r="B20" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,37 +2536,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494778</v>
+        <v>494856</v>
       </c>
       <c r="R20" t="n">
-        <v>6847448</v>
+        <v>6847291</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2610,19 +2610,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123395505</v>
+        <v>123396986</v>
       </c>
       <c r="B21" t="n">
         <v>78525</v>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494727</v>
+        <v>494778</v>
       </c>
       <c r="R21" t="n">
-        <v>6847677</v>
+        <v>6847448</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123398345</v>
+        <v>123403597</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,37 +2740,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494856</v>
+        <v>494804</v>
       </c>
       <c r="R22" t="n">
-        <v>6847291</v>
+        <v>6847196</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2814,22 +2814,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123398038</v>
+        <v>123396886</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,13 +2866,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494836</v>
+        <v>494774</v>
       </c>
       <c r="R23" t="n">
-        <v>6847308</v>
+        <v>6847453</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123403597</v>
+        <v>123398134</v>
       </c>
       <c r="B24" t="n">
-        <v>78433</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2944,21 +2944,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494804</v>
+        <v>494855</v>
       </c>
       <c r="R24" t="n">
-        <v>6847196</v>
+        <v>6847271</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123395906</v>
+        <v>123399650</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,25 +3042,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494732</v>
+        <v>494916</v>
       </c>
       <c r="R25" t="n">
-        <v>6847579</v>
+        <v>6847423</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3120,22 +3120,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123402870</v>
+        <v>123395990</v>
       </c>
       <c r="B26" t="n">
-        <v>98504</v>
+        <v>78524</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,25 +3144,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494829</v>
+        <v>494764</v>
       </c>
       <c r="R26" t="n">
-        <v>6847079</v>
+        <v>6847568</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123397848</v>
+        <v>123395906</v>
       </c>
       <c r="B27" t="n">
-        <v>78433</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,13 +3274,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494825</v>
+        <v>494732</v>
       </c>
       <c r="R27" t="n">
-        <v>6847351</v>
+        <v>6847579</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3324,22 +3324,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123395955</v>
+        <v>123402474</v>
       </c>
       <c r="B28" t="n">
-        <v>78525</v>
+        <v>90990</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,13 +3376,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494764</v>
+        <v>494859</v>
       </c>
       <c r="R28" t="n">
-        <v>6847568</v>
+        <v>6847114</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123398038</v>
+        <v>123398723</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494836</v>
+        <v>494908</v>
       </c>
       <c r="R10" t="n">
-        <v>6847308</v>
+        <v>6847305</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123402561</v>
+        <v>123395626</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494857</v>
+        <v>494727</v>
       </c>
       <c r="R11" t="n">
-        <v>6847085</v>
+        <v>6847673</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,22 +1692,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123398723</v>
+        <v>123398038</v>
       </c>
       <c r="B12" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494908</v>
+        <v>494836</v>
       </c>
       <c r="R12" t="n">
-        <v>6847305</v>
+        <v>6847308</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123395626</v>
+        <v>123402561</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494727</v>
+        <v>494857</v>
       </c>
       <c r="R13" t="n">
-        <v>6847673</v>
+        <v>6847085</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1896,12 +1896,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123398345</v>
+        <v>123396986</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,37 +2536,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494856</v>
+        <v>494778</v>
       </c>
       <c r="R20" t="n">
-        <v>6847291</v>
+        <v>6847448</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2610,22 +2610,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123396986</v>
+        <v>123403597</v>
       </c>
       <c r="B21" t="n">
-        <v>78525</v>
+        <v>78433</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2638,21 +2638,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494778</v>
+        <v>494804</v>
       </c>
       <c r="R21" t="n">
-        <v>6847448</v>
+        <v>6847196</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123403597</v>
+        <v>123398345</v>
       </c>
       <c r="B22" t="n">
-        <v>78433</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,37 +2740,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494804</v>
+        <v>494856</v>
       </c>
       <c r="R22" t="n">
-        <v>6847196</v>
+        <v>6847291</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2814,12 +2814,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123398359</v>
+        <v>123396228</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494882</v>
+        <v>494766</v>
       </c>
       <c r="R2" t="n">
-        <v>6847247</v>
+        <v>6847564</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123395505</v>
+        <v>123395906</v>
       </c>
       <c r="B3" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494727</v>
+        <v>494732</v>
       </c>
       <c r="R3" t="n">
-        <v>6847677</v>
+        <v>6847579</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123397886</v>
+        <v>123403076</v>
       </c>
       <c r="B4" t="n">
-        <v>79870</v>
+        <v>79898</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494832</v>
+        <v>494829</v>
       </c>
       <c r="R4" t="n">
-        <v>6847342</v>
+        <v>6847079</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123397955</v>
+        <v>123398134</v>
       </c>
       <c r="B5" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,37 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494834</v>
+        <v>494855</v>
       </c>
       <c r="R5" t="n">
-        <v>6847337</v>
+        <v>6847271</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123402845</v>
+        <v>123397848</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>78433</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,50 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494845</v>
+        <v>494825</v>
       </c>
       <c r="R6" t="n">
-        <v>6847104</v>
+        <v>6847351</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123398955</v>
+        <v>123396986</v>
       </c>
       <c r="B7" t="n">
-        <v>78524</v>
+        <v>78525</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494898</v>
+        <v>494778</v>
       </c>
       <c r="R7" t="n">
-        <v>6847337</v>
+        <v>6847448</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1296,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123396228</v>
+        <v>123402870</v>
       </c>
       <c r="B8" t="n">
-        <v>79377</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494766</v>
+        <v>494829</v>
       </c>
       <c r="R8" t="n">
-        <v>6847564</v>
+        <v>6847079</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123402463</v>
+        <v>123398359</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494846</v>
+        <v>494882</v>
       </c>
       <c r="R9" t="n">
-        <v>6847218</v>
+        <v>6847247</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1500,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123398723</v>
+        <v>123395626</v>
       </c>
       <c r="B10" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494908</v>
+        <v>494727</v>
       </c>
       <c r="R10" t="n">
-        <v>6847305</v>
+        <v>6847673</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1590,22 +1581,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123395626</v>
+        <v>123402474</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494727</v>
+        <v>494859</v>
       </c>
       <c r="R11" t="n">
-        <v>6847673</v>
+        <v>6847114</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,19 +1683,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123398038</v>
+        <v>123398345</v>
       </c>
       <c r="B12" t="n">
         <v>78788</v>
@@ -1740,17 +1731,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494836</v>
+        <v>494856</v>
       </c>
       <c r="R12" t="n">
-        <v>6847308</v>
+        <v>6847291</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,22 +1785,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123402561</v>
+        <v>123399860</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,41 +1809,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494857</v>
+        <v>494841</v>
       </c>
       <c r="R13" t="n">
-        <v>6847085</v>
+        <v>6847322</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1896,22 +1887,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123399860</v>
+        <v>123396886</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,37 +1915,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494841</v>
+        <v>494774</v>
       </c>
       <c r="R14" t="n">
-        <v>6847322</v>
+        <v>6847453</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1998,22 +1989,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123399373</v>
+        <v>123395505</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,37 +2017,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494944</v>
+        <v>494727</v>
       </c>
       <c r="R15" t="n">
-        <v>6847470</v>
+        <v>6847677</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2100,22 +2091,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123395955</v>
+        <v>123399373</v>
       </c>
       <c r="B16" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,37 +2119,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494764</v>
+        <v>494944</v>
       </c>
       <c r="R16" t="n">
-        <v>6847568</v>
+        <v>6847470</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2202,22 +2193,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123403076</v>
+        <v>123402845</v>
       </c>
       <c r="B17" t="n">
-        <v>79898</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,41 +2217,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494829</v>
+        <v>494845</v>
       </c>
       <c r="R17" t="n">
-        <v>6847079</v>
+        <v>6847104</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2304,22 +2304,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123397848</v>
+        <v>123395990</v>
       </c>
       <c r="B18" t="n">
-        <v>78433</v>
+        <v>78524</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494825</v>
+        <v>494764</v>
       </c>
       <c r="R18" t="n">
-        <v>6847351</v>
+        <v>6847568</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123402870</v>
+        <v>123399650</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>79898</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,25 +2430,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494829</v>
+        <v>494916</v>
       </c>
       <c r="R19" t="n">
-        <v>6847079</v>
+        <v>6847423</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,7 +2520,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123396986</v>
+        <v>123395955</v>
       </c>
       <c r="B20" t="n">
         <v>78525</v>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494778</v>
+        <v>494764</v>
       </c>
       <c r="R20" t="n">
-        <v>6847448</v>
+        <v>6847568</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123403597</v>
+        <v>123402561</v>
       </c>
       <c r="B21" t="n">
-        <v>78433</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,25 +2634,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,13 +2662,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494804</v>
+        <v>494857</v>
       </c>
       <c r="R21" t="n">
-        <v>6847196</v>
+        <v>6847085</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123398345</v>
+        <v>123398723</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,37 +2740,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494856</v>
+        <v>494908</v>
       </c>
       <c r="R22" t="n">
-        <v>6847291</v>
+        <v>6847305</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2814,22 +2814,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123396886</v>
+        <v>123397886</v>
       </c>
       <c r="B23" t="n">
-        <v>78433</v>
+        <v>79870</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,13 +2866,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494774</v>
+        <v>494832</v>
       </c>
       <c r="R23" t="n">
-        <v>6847453</v>
+        <v>6847342</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123398134</v>
+        <v>123397955</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2944,37 +2944,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494855</v>
+        <v>494834</v>
       </c>
       <c r="R24" t="n">
-        <v>6847271</v>
+        <v>6847337</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3018,22 +3018,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123399650</v>
+        <v>123403597</v>
       </c>
       <c r="B25" t="n">
-        <v>79898</v>
+        <v>78433</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,25 +3042,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494916</v>
+        <v>494804</v>
       </c>
       <c r="R25" t="n">
-        <v>6847423</v>
+        <v>6847196</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123395990</v>
+        <v>123402463</v>
       </c>
       <c r="B26" t="n">
-        <v>78524</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,25 +3144,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494764</v>
+        <v>494846</v>
       </c>
       <c r="R26" t="n">
-        <v>6847568</v>
+        <v>6847218</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123395906</v>
+        <v>123398955</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,13 +3274,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494732</v>
+        <v>494898</v>
       </c>
       <c r="R27" t="n">
-        <v>6847579</v>
+        <v>6847337</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3324,22 +3324,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123402474</v>
+        <v>123398038</v>
       </c>
       <c r="B28" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,13 +3376,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494859</v>
+        <v>494836</v>
       </c>
       <c r="R28" t="n">
-        <v>6847114</v>
+        <v>6847308</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123396228</v>
+        <v>123402474</v>
       </c>
       <c r="B2" t="n">
-        <v>79377</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494766</v>
+        <v>494859</v>
       </c>
       <c r="R2" t="n">
-        <v>6847564</v>
+        <v>6847114</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123395906</v>
+        <v>123398359</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494732</v>
+        <v>494882</v>
       </c>
       <c r="R3" t="n">
-        <v>6847579</v>
+        <v>6847247</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123403076</v>
+        <v>123396886</v>
       </c>
       <c r="B4" t="n">
-        <v>79898</v>
+        <v>78433</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494829</v>
+        <v>494774</v>
       </c>
       <c r="R4" t="n">
-        <v>6847079</v>
+        <v>6847453</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123398134</v>
+        <v>123399860</v>
       </c>
       <c r="B5" t="n">
         <v>78788</v>
@@ -1017,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494855</v>
+        <v>494841</v>
       </c>
       <c r="R5" t="n">
-        <v>6847271</v>
+        <v>6847322</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123397848</v>
+        <v>123398723</v>
       </c>
       <c r="B6" t="n">
-        <v>78433</v>
+        <v>78524</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494825</v>
+        <v>494908</v>
       </c>
       <c r="R6" t="n">
-        <v>6847351</v>
+        <v>6847305</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123396986</v>
+        <v>123403597</v>
       </c>
       <c r="B7" t="n">
-        <v>78525</v>
+        <v>78433</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494778</v>
+        <v>494804</v>
       </c>
       <c r="R7" t="n">
-        <v>6847448</v>
+        <v>6847196</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123402870</v>
+        <v>123398345</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,41 +1299,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494829</v>
+        <v>494856</v>
       </c>
       <c r="R8" t="n">
-        <v>6847079</v>
+        <v>6847291</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,19 +1377,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123398359</v>
+        <v>123395626</v>
       </c>
       <c r="B9" t="n">
         <v>78788</v>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494882</v>
+        <v>494727</v>
       </c>
       <c r="R9" t="n">
-        <v>6847247</v>
+        <v>6847673</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,19 +1479,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123395626</v>
+        <v>123395906</v>
       </c>
       <c r="B10" t="n">
         <v>78788</v>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494727</v>
+        <v>494732</v>
       </c>
       <c r="R10" t="n">
-        <v>6847673</v>
+        <v>6847579</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123402474</v>
+        <v>123398955</v>
       </c>
       <c r="B11" t="n">
-        <v>90990</v>
+        <v>78524</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494859</v>
+        <v>494898</v>
       </c>
       <c r="R11" t="n">
-        <v>6847114</v>
+        <v>6847337</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123398345</v>
+        <v>123395505</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,37 +1711,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494856</v>
+        <v>494727</v>
       </c>
       <c r="R12" t="n">
-        <v>6847291</v>
+        <v>6847677</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,22 +1785,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123399860</v>
+        <v>123402561</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,41 +1809,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494841</v>
+        <v>494857</v>
       </c>
       <c r="R13" t="n">
-        <v>6847322</v>
+        <v>6847085</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1887,22 +1887,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123396886</v>
+        <v>123396228</v>
       </c>
       <c r="B14" t="n">
-        <v>78433</v>
+        <v>79377</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494774</v>
+        <v>494766</v>
       </c>
       <c r="R14" t="n">
-        <v>6847453</v>
+        <v>6847564</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123395505</v>
+        <v>123395990</v>
       </c>
       <c r="B15" t="n">
-        <v>78525</v>
+        <v>78524</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494727</v>
+        <v>494764</v>
       </c>
       <c r="R15" t="n">
-        <v>6847677</v>
+        <v>6847568</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123399373</v>
+        <v>123402845</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,38 +2115,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494944</v>
+        <v>494845</v>
       </c>
       <c r="R16" t="n">
-        <v>6847470</v>
+        <v>6847104</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123402845</v>
+        <v>123399373</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,47 +2226,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494845</v>
+        <v>494944</v>
       </c>
       <c r="R17" t="n">
-        <v>6847104</v>
+        <v>6847470</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123395990</v>
+        <v>123403076</v>
       </c>
       <c r="B18" t="n">
-        <v>78524</v>
+        <v>79898</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,25 +2328,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494764</v>
+        <v>494829</v>
       </c>
       <c r="R18" t="n">
-        <v>6847568</v>
+        <v>6847079</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123399650</v>
+        <v>123395955</v>
       </c>
       <c r="B19" t="n">
-        <v>79898</v>
+        <v>78525</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,25 +2430,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494916</v>
+        <v>494764</v>
       </c>
       <c r="R19" t="n">
-        <v>6847423</v>
+        <v>6847568</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123395955</v>
+        <v>123398038</v>
       </c>
       <c r="B20" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494764</v>
+        <v>494836</v>
       </c>
       <c r="R20" t="n">
-        <v>6847568</v>
+        <v>6847308</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123402561</v>
+        <v>123402870</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494857</v>
+        <v>494829</v>
       </c>
       <c r="R21" t="n">
-        <v>6847085</v>
+        <v>6847079</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123398723</v>
+        <v>123396986</v>
       </c>
       <c r="B22" t="n">
-        <v>78524</v>
+        <v>78525</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494908</v>
+        <v>494778</v>
       </c>
       <c r="R22" t="n">
-        <v>6847305</v>
+        <v>6847448</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123397886</v>
+        <v>123398134</v>
       </c>
       <c r="B23" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494832</v>
+        <v>494855</v>
       </c>
       <c r="R23" t="n">
-        <v>6847342</v>
+        <v>6847271</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123397955</v>
+        <v>123399650</v>
       </c>
       <c r="B24" t="n">
-        <v>78525</v>
+        <v>79898</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,41 +2940,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494834</v>
+        <v>494916</v>
       </c>
       <c r="R24" t="n">
-        <v>6847337</v>
+        <v>6847423</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3018,22 +3018,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123403597</v>
+        <v>123402463</v>
       </c>
       <c r="B25" t="n">
-        <v>78433</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,25 +3042,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494804</v>
+        <v>494846</v>
       </c>
       <c r="R25" t="n">
-        <v>6847196</v>
+        <v>6847218</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123402463</v>
+        <v>123397955</v>
       </c>
       <c r="B26" t="n">
-        <v>98079</v>
+        <v>78525</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,41 +3144,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494846</v>
+        <v>494834</v>
       </c>
       <c r="R26" t="n">
-        <v>6847218</v>
+        <v>6847337</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3222,22 +3222,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123398955</v>
+        <v>123397886</v>
       </c>
       <c r="B27" t="n">
-        <v>78524</v>
+        <v>79870</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494898</v>
+        <v>494832</v>
       </c>
       <c r="R27" t="n">
-        <v>6847337</v>
+        <v>6847342</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123398038</v>
+        <v>123397848</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494836</v>
+        <v>494825</v>
       </c>
       <c r="R28" t="n">
-        <v>6847308</v>
+        <v>6847351</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123402474</v>
+        <v>123402463</v>
       </c>
       <c r="B2" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494859</v>
+        <v>494846</v>
       </c>
       <c r="R2" t="n">
-        <v>6847114</v>
+        <v>6847218</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123396886</v>
+        <v>123397955</v>
       </c>
       <c r="B4" t="n">
-        <v>78433</v>
+        <v>78525</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494774</v>
+        <v>494834</v>
       </c>
       <c r="R4" t="n">
-        <v>6847453</v>
+        <v>6847337</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,12 +969,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123398723</v>
+        <v>123396228</v>
       </c>
       <c r="B6" t="n">
-        <v>78524</v>
+        <v>79377</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494908</v>
+        <v>494766</v>
       </c>
       <c r="R6" t="n">
-        <v>6847305</v>
+        <v>6847564</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123403597</v>
+        <v>123397886</v>
       </c>
       <c r="B7" t="n">
-        <v>78433</v>
+        <v>79870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494804</v>
+        <v>494832</v>
       </c>
       <c r="R7" t="n">
-        <v>6847196</v>
+        <v>6847342</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123398345</v>
+        <v>123402845</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,41 +1299,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494856</v>
+        <v>494845</v>
       </c>
       <c r="R8" t="n">
-        <v>6847291</v>
+        <v>6847104</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123395626</v>
+        <v>123398345</v>
       </c>
       <c r="B9" t="n">
         <v>78788</v>
@@ -1425,17 +1434,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494727</v>
+        <v>494856</v>
       </c>
       <c r="R9" t="n">
-        <v>6847673</v>
+        <v>6847291</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123395906</v>
+        <v>123395505</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,13 +1540,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494732</v>
+        <v>494727</v>
       </c>
       <c r="R10" t="n">
-        <v>6847579</v>
+        <v>6847677</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,22 +1590,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123398955</v>
+        <v>123402870</v>
       </c>
       <c r="B11" t="n">
-        <v>78524</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1642,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494898</v>
+        <v>494829</v>
       </c>
       <c r="R11" t="n">
-        <v>6847337</v>
+        <v>6847079</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,7 +1704,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123395505</v>
+        <v>123395955</v>
       </c>
       <c r="B12" t="n">
         <v>78525</v>
@@ -1735,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494727</v>
+        <v>494764</v>
       </c>
       <c r="R12" t="n">
-        <v>6847677</v>
+        <v>6847568</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1797,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123402561</v>
+        <v>123402474</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494857</v>
+        <v>494859</v>
       </c>
       <c r="R13" t="n">
-        <v>6847085</v>
+        <v>6847114</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123396228</v>
+        <v>123395626</v>
       </c>
       <c r="B14" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494766</v>
+        <v>494727</v>
       </c>
       <c r="R14" t="n">
-        <v>6847564</v>
+        <v>6847673</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,19 +1998,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123395990</v>
+        <v>123398723</v>
       </c>
       <c r="B15" t="n">
         <v>78524</v>
@@ -2041,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494764</v>
+        <v>494908</v>
       </c>
       <c r="R15" t="n">
-        <v>6847568</v>
+        <v>6847305</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2103,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123402845</v>
+        <v>123399650</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
+        <v>79898</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,47 +2124,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494845</v>
+        <v>494916</v>
       </c>
       <c r="R16" t="n">
-        <v>6847104</v>
+        <v>6847423</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,19 +2202,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123399373</v>
+        <v>123398038</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2250,17 +2250,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494944</v>
+        <v>494836</v>
       </c>
       <c r="R17" t="n">
-        <v>6847470</v>
+        <v>6847308</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2304,22 +2304,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123403076</v>
+        <v>123402561</v>
       </c>
       <c r="B18" t="n">
-        <v>79898</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,25 +2328,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,13 +2356,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494829</v>
+        <v>494857</v>
       </c>
       <c r="R18" t="n">
-        <v>6847079</v>
+        <v>6847085</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123395955</v>
+        <v>123395906</v>
       </c>
       <c r="B19" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494764</v>
+        <v>494732</v>
       </c>
       <c r="R19" t="n">
-        <v>6847568</v>
+        <v>6847579</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2508,22 +2508,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123398038</v>
+        <v>123396886</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494836</v>
+        <v>494774</v>
       </c>
       <c r="R20" t="n">
-        <v>6847308</v>
+        <v>6847453</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123402870</v>
+        <v>123398955</v>
       </c>
       <c r="B21" t="n">
-        <v>98079</v>
+        <v>78524</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,25 +2634,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,13 +2662,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494829</v>
+        <v>494898</v>
       </c>
       <c r="R21" t="n">
-        <v>6847079</v>
+        <v>6847337</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123396986</v>
+        <v>123399373</v>
       </c>
       <c r="B22" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,37 +2740,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494778</v>
+        <v>494944</v>
       </c>
       <c r="R22" t="n">
-        <v>6847448</v>
+        <v>6847470</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2814,22 +2814,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123398134</v>
+        <v>123395990</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494855</v>
+        <v>494764</v>
       </c>
       <c r="R23" t="n">
-        <v>6847271</v>
+        <v>6847568</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123399650</v>
+        <v>123398134</v>
       </c>
       <c r="B24" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,25 +2940,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494916</v>
+        <v>494855</v>
       </c>
       <c r="R24" t="n">
-        <v>6847423</v>
+        <v>6847271</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123402463</v>
+        <v>123397848</v>
       </c>
       <c r="B25" t="n">
-        <v>98079</v>
+        <v>78433</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,25 +3042,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494846</v>
+        <v>494825</v>
       </c>
       <c r="R25" t="n">
-        <v>6847218</v>
+        <v>6847351</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123397955</v>
+        <v>123403076</v>
       </c>
       <c r="B26" t="n">
-        <v>78525</v>
+        <v>79898</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,41 +3144,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494834</v>
+        <v>494829</v>
       </c>
       <c r="R26" t="n">
-        <v>6847337</v>
+        <v>6847079</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3222,22 +3222,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123397886</v>
+        <v>123403597</v>
       </c>
       <c r="B27" t="n">
-        <v>79870</v>
+        <v>78433</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494832</v>
+        <v>494804</v>
       </c>
       <c r="R27" t="n">
-        <v>6847342</v>
+        <v>6847196</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123397848</v>
+        <v>123396986</v>
       </c>
       <c r="B28" t="n">
-        <v>78433</v>
+        <v>78525</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494825</v>
+        <v>494778</v>
       </c>
       <c r="R28" t="n">
-        <v>6847351</v>
+        <v>6847448</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123397886</v>
+        <v>123398345</v>
       </c>
       <c r="B7" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494832</v>
+        <v>494856</v>
       </c>
       <c r="R7" t="n">
-        <v>6847342</v>
+        <v>6847291</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123402845</v>
+        <v>123395505</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>78525</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,50 +1299,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494845</v>
+        <v>494727</v>
       </c>
       <c r="R8" t="n">
-        <v>6847104</v>
+        <v>6847677</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123398345</v>
+        <v>123402845</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,41 +1401,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494856</v>
+        <v>494845</v>
       </c>
       <c r="R9" t="n">
-        <v>6847291</v>
+        <v>6847104</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123395505</v>
+        <v>123397886</v>
       </c>
       <c r="B10" t="n">
-        <v>78525</v>
+        <v>79870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494727</v>
+        <v>494832</v>
       </c>
       <c r="R10" t="n">
-        <v>6847677</v>
+        <v>6847342</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123399650</v>
+        <v>123402561</v>
       </c>
       <c r="B16" t="n">
-        <v>79898</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,25 +2124,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494916</v>
+        <v>494857</v>
       </c>
       <c r="R16" t="n">
-        <v>6847423</v>
+        <v>6847085</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123398038</v>
+        <v>123399650</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,25 +2226,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,13 +2254,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494836</v>
+        <v>494916</v>
       </c>
       <c r="R17" t="n">
-        <v>6847308</v>
+        <v>6847423</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123402561</v>
+        <v>123398038</v>
       </c>
       <c r="B18" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,25 +2328,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,13 +2356,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494857</v>
+        <v>494836</v>
       </c>
       <c r="R18" t="n">
-        <v>6847085</v>
+        <v>6847308</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123402463</v>
+        <v>123398345</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494846</v>
+        <v>494856</v>
       </c>
       <c r="R2" t="n">
-        <v>6847218</v>
+        <v>6847291</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123398359</v>
+        <v>123397886</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494882</v>
+        <v>494832</v>
       </c>
       <c r="R3" t="n">
-        <v>6847247</v>
+        <v>6847342</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123397955</v>
+        <v>123396228</v>
       </c>
       <c r="B4" t="n">
-        <v>78525</v>
+        <v>79377</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494834</v>
+        <v>494766</v>
       </c>
       <c r="R4" t="n">
-        <v>6847337</v>
+        <v>6847564</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,19 +969,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123399860</v>
+        <v>123398038</v>
       </c>
       <c r="B5" t="n">
         <v>78788</v>
@@ -1017,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494841</v>
+        <v>494836</v>
       </c>
       <c r="R5" t="n">
-        <v>6847322</v>
+        <v>6847308</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123396228</v>
+        <v>123402561</v>
       </c>
       <c r="B6" t="n">
-        <v>79377</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494766</v>
+        <v>494857</v>
       </c>
       <c r="R6" t="n">
-        <v>6847564</v>
+        <v>6847085</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123398345</v>
+        <v>123397848</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494856</v>
+        <v>494825</v>
       </c>
       <c r="R7" t="n">
-        <v>6847291</v>
+        <v>6847351</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123395505</v>
+        <v>123399860</v>
       </c>
       <c r="B8" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,37 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494727</v>
+        <v>494841</v>
       </c>
       <c r="R8" t="n">
-        <v>6847677</v>
+        <v>6847322</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123402845</v>
+        <v>123397955</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>78525</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,50 +1401,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494845</v>
+        <v>494834</v>
       </c>
       <c r="R9" t="n">
-        <v>6847104</v>
+        <v>6847337</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123397886</v>
+        <v>123395505</v>
       </c>
       <c r="B10" t="n">
-        <v>79870</v>
+        <v>78525</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494832</v>
+        <v>494727</v>
       </c>
       <c r="R10" t="n">
-        <v>6847342</v>
+        <v>6847677</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1602,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123402870</v>
+        <v>123402845</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1635,17 +1626,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494829</v>
+        <v>494845</v>
       </c>
       <c r="R11" t="n">
-        <v>6847079</v>
+        <v>6847104</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,22 +1692,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123395955</v>
+        <v>123396886</v>
       </c>
       <c r="B12" t="n">
-        <v>78525</v>
+        <v>78433</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,13 +1744,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494764</v>
+        <v>494774</v>
       </c>
       <c r="R12" t="n">
-        <v>6847568</v>
+        <v>6847453</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123402474</v>
+        <v>123402463</v>
       </c>
       <c r="B13" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,13 +1846,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494859</v>
+        <v>494846</v>
       </c>
       <c r="R13" t="n">
-        <v>6847114</v>
+        <v>6847218</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123395626</v>
+        <v>123395906</v>
       </c>
       <c r="B14" t="n">
         <v>78788</v>
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494727</v>
+        <v>494732</v>
       </c>
       <c r="R14" t="n">
-        <v>6847673</v>
+        <v>6847579</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123398723</v>
+        <v>123399650</v>
       </c>
       <c r="B15" t="n">
-        <v>78524</v>
+        <v>79898</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,25 +2022,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,13 +2050,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494908</v>
+        <v>494916</v>
       </c>
       <c r="R15" t="n">
-        <v>6847305</v>
+        <v>6847423</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123402561</v>
+        <v>123398723</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
+        <v>78524</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,25 +2124,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494857</v>
+        <v>494908</v>
       </c>
       <c r="R16" t="n">
-        <v>6847085</v>
+        <v>6847305</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123399650</v>
+        <v>123403597</v>
       </c>
       <c r="B17" t="n">
-        <v>79898</v>
+        <v>78433</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,25 +2226,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,13 +2254,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494916</v>
+        <v>494804</v>
       </c>
       <c r="R17" t="n">
-        <v>6847423</v>
+        <v>6847196</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123398038</v>
+        <v>123395990</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494836</v>
+        <v>494764</v>
       </c>
       <c r="R18" t="n">
-        <v>6847308</v>
+        <v>6847568</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123395906</v>
+        <v>123396986</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494732</v>
+        <v>494778</v>
       </c>
       <c r="R19" t="n">
-        <v>6847579</v>
+        <v>6847448</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2508,22 +2508,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123396886</v>
+        <v>123395626</v>
       </c>
       <c r="B20" t="n">
-        <v>78433</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494774</v>
+        <v>494727</v>
       </c>
       <c r="R20" t="n">
-        <v>6847453</v>
+        <v>6847673</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2610,22 +2610,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123398955</v>
+        <v>123403076</v>
       </c>
       <c r="B21" t="n">
-        <v>78524</v>
+        <v>79898</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,25 +2634,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494898</v>
+        <v>494829</v>
       </c>
       <c r="R21" t="n">
-        <v>6847337</v>
+        <v>6847079</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123399373</v>
+        <v>123398134</v>
       </c>
       <c r="B22" t="n">
         <v>78788</v>
@@ -2760,17 +2760,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494944</v>
+        <v>494855</v>
       </c>
       <c r="R22" t="n">
-        <v>6847470</v>
+        <v>6847271</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2814,22 +2814,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123395990</v>
+        <v>123395955</v>
       </c>
       <c r="B23" t="n">
-        <v>78524</v>
+        <v>78525</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123398134</v>
+        <v>123398955</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2944,21 +2944,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494855</v>
+        <v>494898</v>
       </c>
       <c r="R24" t="n">
-        <v>6847271</v>
+        <v>6847337</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123397848</v>
+        <v>123398359</v>
       </c>
       <c r="B25" t="n">
-        <v>78433</v>
+        <v>78788</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494825</v>
+        <v>494882</v>
       </c>
       <c r="R25" t="n">
-        <v>6847351</v>
+        <v>6847247</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123403076</v>
+        <v>123399373</v>
       </c>
       <c r="B26" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,41 +3144,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494829</v>
+        <v>494944</v>
       </c>
       <c r="R26" t="n">
-        <v>6847079</v>
+        <v>6847470</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3222,22 +3222,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123403597</v>
+        <v>123402474</v>
       </c>
       <c r="B27" t="n">
-        <v>78433</v>
+        <v>90990</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,13 +3274,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494804</v>
+        <v>494859</v>
       </c>
       <c r="R27" t="n">
-        <v>6847196</v>
+        <v>6847114</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123396986</v>
+        <v>123402870</v>
       </c>
       <c r="B28" t="n">
-        <v>78525</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,25 +3348,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,13 +3376,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494778</v>
+        <v>494829</v>
       </c>
       <c r="R28" t="n">
-        <v>6847448</v>
+        <v>6847079</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3438,7 +3438,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124431969</v>
+        <v>124432056</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3471,26 +3471,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494837</v>
+        <v>494859</v>
       </c>
       <c r="R29" t="n">
-        <v>6847108</v>
+        <v>6847061</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3651,7 +3642,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124432127</v>
+        <v>124431969</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3686,7 +3677,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3700,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494854</v>
+        <v>494837</v>
       </c>
       <c r="R31" t="n">
-        <v>6847009</v>
+        <v>6847108</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3762,7 +3753,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124432056</v>
+        <v>124432127</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -3795,17 +3786,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494859</v>
+        <v>494854</v>
       </c>
       <c r="R32" t="n">
-        <v>6847061</v>
+        <v>6847009</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124431907</v>
+        <v>124431969</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,38 +3552,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494819</v>
+        <v>494837</v>
       </c>
       <c r="R30" t="n">
-        <v>6847117</v>
+        <v>6847108</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3642,10 +3651,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124431969</v>
+        <v>124431907</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3654,47 +3663,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494837</v>
+        <v>494819</v>
       </c>
       <c r="R31" t="n">
-        <v>6847108</v>
+        <v>6847117</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124432056</v>
+        <v>124431907</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,25 +3450,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494859</v>
+        <v>494819</v>
       </c>
       <c r="R29" t="n">
-        <v>6847061</v>
+        <v>6847117</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3540,7 +3540,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124431969</v>
+        <v>124432127</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494837</v>
+        <v>494854</v>
       </c>
       <c r="R30" t="n">
-        <v>6847108</v>
+        <v>6847009</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124431907</v>
+        <v>124431969</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3663,38 +3663,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494819</v>
+        <v>494837</v>
       </c>
       <c r="R31" t="n">
-        <v>6847117</v>
+        <v>6847108</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3753,7 +3762,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124432127</v>
+        <v>124432056</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -3786,26 +3795,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494854</v>
+        <v>494859</v>
       </c>
       <c r="R32" t="n">
-        <v>6847009</v>
+        <v>6847061</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3540,7 +3540,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124432127</v>
+        <v>124431969</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494854</v>
+        <v>494837</v>
       </c>
       <c r="R30" t="n">
-        <v>6847009</v>
+        <v>6847108</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3651,7 +3651,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124431969</v>
+        <v>124432056</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3684,26 +3684,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494837</v>
+        <v>494859</v>
       </c>
       <c r="R31" t="n">
-        <v>6847108</v>
+        <v>6847061</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3762,7 +3753,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124432056</v>
+        <v>124432127</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -3795,17 +3786,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494859</v>
+        <v>494854</v>
       </c>
       <c r="R32" t="n">
-        <v>6847061</v>
+        <v>6847009</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124431907</v>
+        <v>124432056</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,25 +3450,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494819</v>
+        <v>494859</v>
       </c>
       <c r="R29" t="n">
-        <v>6847117</v>
+        <v>6847061</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3651,7 +3651,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124432056</v>
+        <v>124432127</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3684,17 +3684,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494859</v>
+        <v>494854</v>
       </c>
       <c r="R31" t="n">
-        <v>6847061</v>
+        <v>6847009</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3753,10 +3762,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124432127</v>
+        <v>124431907</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3765,47 +3774,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494854</v>
+        <v>494819</v>
       </c>
       <c r="R32" t="n">
-        <v>6847009</v>
+        <v>6847117</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3438,7 +3438,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124432056</v>
+        <v>124432127</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3471,17 +3471,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494859</v>
+        <v>494854</v>
       </c>
       <c r="R29" t="n">
-        <v>6847061</v>
+        <v>6847009</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3651,10 +3660,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124432127</v>
+        <v>124431907</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3663,47 +3672,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494854</v>
+        <v>494819</v>
       </c>
       <c r="R31" t="n">
-        <v>6847009</v>
+        <v>6847117</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124431907</v>
+        <v>124432056</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3774,25 +3774,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494819</v>
+        <v>494859</v>
       </c>
       <c r="R32" t="n">
-        <v>6847117</v>
+        <v>6847061</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3438,7 +3438,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124432127</v>
+        <v>124431969</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494854</v>
+        <v>494837</v>
       </c>
       <c r="R29" t="n">
-        <v>6847009</v>
+        <v>6847108</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3549,7 +3549,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124431969</v>
+        <v>124432056</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3582,26 +3582,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494837</v>
+        <v>494859</v>
       </c>
       <c r="R30" t="n">
-        <v>6847108</v>
+        <v>6847061</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3762,7 +3753,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124432056</v>
+        <v>124432127</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -3795,17 +3786,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494859</v>
+        <v>494854</v>
       </c>
       <c r="R32" t="n">
-        <v>6847061</v>
+        <v>6847009</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124431969</v>
+        <v>124431907</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,47 +3450,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494837</v>
+        <v>494819</v>
       </c>
       <c r="R29" t="n">
-        <v>6847108</v>
+        <v>6847117</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3549,7 +3540,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124432056</v>
+        <v>124432127</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3582,17 +3573,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494859</v>
+        <v>494854</v>
       </c>
       <c r="R30" t="n">
-        <v>6847061</v>
+        <v>6847009</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124431907</v>
+        <v>124432056</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3663,25 +3663,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494819</v>
+        <v>494859</v>
       </c>
       <c r="R31" t="n">
-        <v>6847117</v>
+        <v>6847061</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124432127</v>
+        <v>124431969</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494854</v>
+        <v>494837</v>
       </c>
       <c r="R32" t="n">
-        <v>6847009</v>
+        <v>6847108</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124431907</v>
+        <v>124431969</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,38 +3450,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494819</v>
+        <v>494837</v>
       </c>
       <c r="R29" t="n">
-        <v>6847117</v>
+        <v>6847108</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3540,10 +3549,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124432127</v>
+        <v>124431907</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,47 +3561,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494854</v>
+        <v>494819</v>
       </c>
       <c r="R30" t="n">
-        <v>6847009</v>
+        <v>6847117</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124431969</v>
+        <v>124432127</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494837</v>
+        <v>494854</v>
       </c>
       <c r="R32" t="n">
-        <v>6847108</v>
+        <v>6847009</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3549,10 +3549,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124431907</v>
+        <v>124432056</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3561,25 +3561,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494819</v>
+        <v>494859</v>
       </c>
       <c r="R30" t="n">
-        <v>6847117</v>
+        <v>6847061</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124432056</v>
+        <v>124431907</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3663,25 +3663,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494859</v>
+        <v>494819</v>
       </c>
       <c r="R31" t="n">
-        <v>6847061</v>
+        <v>6847117</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3438,7 +3438,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124431969</v>
+        <v>124432127</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494837</v>
+        <v>494854</v>
       </c>
       <c r="R29" t="n">
-        <v>6847108</v>
+        <v>6847009</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3549,7 +3549,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124432056</v>
+        <v>124431969</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3582,17 +3582,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494859</v>
+        <v>494837</v>
       </c>
       <c r="R30" t="n">
-        <v>6847061</v>
+        <v>6847108</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3753,7 +3762,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124432127</v>
+        <v>124432056</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -3786,26 +3795,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494854</v>
+        <v>494859</v>
       </c>
       <c r="R32" t="n">
-        <v>6847009</v>
+        <v>6847061</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3438,7 +3438,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124432127</v>
+        <v>124432056</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3471,26 +3471,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494854</v>
+        <v>494859</v>
       </c>
       <c r="R29" t="n">
-        <v>6847009</v>
+        <v>6847061</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3549,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124431969</v>
+        <v>124431907</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3561,47 +3552,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494837</v>
+        <v>494819</v>
       </c>
       <c r="R30" t="n">
-        <v>6847108</v>
+        <v>6847117</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3660,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124431907</v>
+        <v>124432127</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3672,38 +3654,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494819</v>
+        <v>494854</v>
       </c>
       <c r="R31" t="n">
-        <v>6847117</v>
+        <v>6847009</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3762,7 +3753,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124432056</v>
+        <v>124431969</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -3795,17 +3786,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494859</v>
+        <v>494837</v>
       </c>
       <c r="R32" t="n">
-        <v>6847061</v>
+        <v>6847108</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124431907</v>
+        <v>124431969</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,38 +3552,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494819</v>
+        <v>494837</v>
       </c>
       <c r="R30" t="n">
-        <v>6847117</v>
+        <v>6847108</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3642,10 +3651,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124432127</v>
+        <v>124431907</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3654,47 +3663,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494854</v>
+        <v>494819</v>
       </c>
       <c r="R31" t="n">
-        <v>6847009</v>
+        <v>6847117</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124431969</v>
+        <v>124432127</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494837</v>
+        <v>494854</v>
       </c>
       <c r="R32" t="n">
-        <v>6847108</v>
+        <v>6847009</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3862,6 +3862,1082 @@
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125920678</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98328</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>494852</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6847042</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125920385</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>494890</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6846985</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125920281</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>494845</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6846968</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125921495</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98328</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>494839</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6847211</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125920499</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>494871</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6847013</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125920758</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98328</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>494847</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6847046</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125921522</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98328</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>494840</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6847209</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125920924</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98328</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>494851</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6847070</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125920975</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98328</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>494843</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6847097</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125921363</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>494825</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6847192</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125921474</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98328</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>494832</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6847214</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3864,32 +3864,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125920678</v>
+        <v>125920385</v>
       </c>
       <c r="B33" t="n">
-        <v>98328</v>
+        <v>78967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494852</v>
+        <v>494890</v>
       </c>
       <c r="R33" t="n">
-        <v>6847042</v>
+        <v>6846985</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3961,32 +3961,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125920385</v>
+        <v>125920678</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494890</v>
+        <v>494852</v>
       </c>
       <c r="R34" t="n">
-        <v>6846985</v>
+        <v>6847042</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4158,7 +4158,7 @@
         <v>125921495</v>
       </c>
       <c r="B36" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4252,32 +4252,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125920499</v>
+        <v>125920758</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,13 +4287,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494871</v>
+        <v>494847</v>
       </c>
       <c r="R37" t="n">
-        <v>6847013</v>
+        <v>6847046</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4349,32 +4349,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125920758</v>
+        <v>125920499</v>
       </c>
       <c r="B38" t="n">
-        <v>98328</v>
+        <v>78967</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494847</v>
+        <v>494871</v>
       </c>
       <c r="R38" t="n">
-        <v>6847046</v>
+        <v>6847013</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>125921522</v>
       </c>
       <c r="B39" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4543,10 +4543,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125920924</v>
+        <v>125920975</v>
       </c>
       <c r="B40" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494851</v>
+        <v>494843</v>
       </c>
       <c r="R40" t="n">
-        <v>6847070</v>
+        <v>6847097</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4640,10 +4640,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125920975</v>
+        <v>125920924</v>
       </c>
       <c r="B41" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494843</v>
+        <v>494851</v>
       </c>
       <c r="R41" t="n">
-        <v>6847097</v>
+        <v>6847070</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4837,7 +4837,7 @@
         <v>125921474</v>
       </c>
       <c r="B43" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3867,7 +3867,7 @@
         <v>125920385</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>125920678</v>
       </c>
       <c r="B34" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>125920281</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>125921495</v>
       </c>
       <c r="B36" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4252,32 +4252,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125920758</v>
+        <v>125920499</v>
       </c>
       <c r="B37" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,13 +4287,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494847</v>
+        <v>494871</v>
       </c>
       <c r="R37" t="n">
-        <v>6847046</v>
+        <v>6847013</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4349,32 +4349,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125920499</v>
+        <v>125920758</v>
       </c>
       <c r="B38" t="n">
-        <v>78967</v>
+        <v>98332</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494871</v>
+        <v>494847</v>
       </c>
       <c r="R38" t="n">
-        <v>6847013</v>
+        <v>6847046</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>125921522</v>
       </c>
       <c r="B39" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>125920975</v>
       </c>
       <c r="B40" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>125920924</v>
       </c>
       <c r="B41" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>125921363</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>125921474</v>
       </c>
       <c r="B43" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3964,7 +3964,7 @@
         <v>125920678</v>
       </c>
       <c r="B34" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>125921495</v>
       </c>
       <c r="B36" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4252,32 +4252,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125920499</v>
+        <v>125920758</v>
       </c>
       <c r="B37" t="n">
-        <v>78968</v>
+        <v>98334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,13 +4287,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494871</v>
+        <v>494847</v>
       </c>
       <c r="R37" t="n">
-        <v>6847013</v>
+        <v>6847046</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4349,32 +4349,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125920758</v>
+        <v>125920499</v>
       </c>
       <c r="B38" t="n">
-        <v>98332</v>
+        <v>78968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494847</v>
+        <v>494871</v>
       </c>
       <c r="R38" t="n">
-        <v>6847046</v>
+        <v>6847013</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>125921522</v>
       </c>
       <c r="B39" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>125920975</v>
       </c>
       <c r="B40" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>125920924</v>
       </c>
       <c r="B41" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>125921474</v>
       </c>
       <c r="B43" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3867,7 +3867,7 @@
         <v>125920385</v>
       </c>
       <c r="B33" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>125920678</v>
       </c>
       <c r="B34" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>125920281</v>
       </c>
       <c r="B35" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>125921495</v>
       </c>
       <c r="B36" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4252,32 +4252,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125920758</v>
+        <v>125920499</v>
       </c>
       <c r="B37" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,13 +4287,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494847</v>
+        <v>494871</v>
       </c>
       <c r="R37" t="n">
-        <v>6847046</v>
+        <v>6847013</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4349,32 +4349,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125920499</v>
+        <v>125920758</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494871</v>
+        <v>494847</v>
       </c>
       <c r="R38" t="n">
-        <v>6847013</v>
+        <v>6847046</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>125921522</v>
       </c>
       <c r="B39" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4543,10 +4543,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125920975</v>
+        <v>125920924</v>
       </c>
       <c r="B40" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494843</v>
+        <v>494851</v>
       </c>
       <c r="R40" t="n">
-        <v>6847097</v>
+        <v>6847070</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4640,10 +4640,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125920924</v>
+        <v>125920975</v>
       </c>
       <c r="B41" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494851</v>
+        <v>494843</v>
       </c>
       <c r="R41" t="n">
-        <v>6847070</v>
+        <v>6847097</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4740,7 +4740,7 @@
         <v>125921363</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>125921474</v>
       </c>
       <c r="B43" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3864,32 +3864,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125920385</v>
+        <v>125920678</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>98338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494890</v>
+        <v>494852</v>
       </c>
       <c r="R33" t="n">
-        <v>6846985</v>
+        <v>6847042</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3961,32 +3961,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125920678</v>
+        <v>125920385</v>
       </c>
       <c r="B34" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494852</v>
+        <v>494890</v>
       </c>
       <c r="R34" t="n">
-        <v>6847042</v>
+        <v>6846985</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4543,7 +4543,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125920924</v>
+        <v>125920975</v>
       </c>
       <c r="B40" t="n">
         <v>98338</v>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494851</v>
+        <v>494843</v>
       </c>
       <c r="R40" t="n">
-        <v>6847070</v>
+        <v>6847097</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4640,7 +4640,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125920975</v>
+        <v>125920924</v>
       </c>
       <c r="B41" t="n">
         <v>98338</v>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494843</v>
+        <v>494851</v>
       </c>
       <c r="R41" t="n">
-        <v>6847097</v>
+        <v>6847070</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3867,7 +3867,7 @@
         <v>125920678</v>
       </c>
       <c r="B33" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>125921495</v>
       </c>
       <c r="B36" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4252,32 +4252,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125920499</v>
+        <v>125920758</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,13 +4287,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494871</v>
+        <v>494847</v>
       </c>
       <c r="R37" t="n">
-        <v>6847013</v>
+        <v>6847046</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4349,32 +4349,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125920758</v>
+        <v>125920499</v>
       </c>
       <c r="B38" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494847</v>
+        <v>494871</v>
       </c>
       <c r="R38" t="n">
-        <v>6847046</v>
+        <v>6847013</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>125921522</v>
       </c>
       <c r="B39" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>125920975</v>
       </c>
       <c r="B40" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>125920924</v>
       </c>
       <c r="B41" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>125921474</v>
       </c>
       <c r="B43" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3864,32 +3864,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125920678</v>
+        <v>125920385</v>
       </c>
       <c r="B33" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494852</v>
+        <v>494890</v>
       </c>
       <c r="R33" t="n">
-        <v>6847042</v>
+        <v>6846985</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3961,32 +3961,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125920385</v>
+        <v>125920678</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494890</v>
+        <v>494852</v>
       </c>
       <c r="R34" t="n">
-        <v>6846985</v>
+        <v>6847042</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3864,32 +3864,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125920385</v>
+        <v>125920678</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494890</v>
+        <v>494852</v>
       </c>
       <c r="R33" t="n">
-        <v>6846985</v>
+        <v>6847042</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3961,32 +3961,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125920678</v>
+        <v>125920385</v>
       </c>
       <c r="B34" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494852</v>
+        <v>494890</v>
       </c>
       <c r="R34" t="n">
-        <v>6847042</v>
+        <v>6846985</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4252,32 +4252,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125920758</v>
+        <v>125920499</v>
       </c>
       <c r="B37" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,13 +4287,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494847</v>
+        <v>494871</v>
       </c>
       <c r="R37" t="n">
-        <v>6847046</v>
+        <v>6847013</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4349,32 +4349,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125920499</v>
+        <v>125920758</v>
       </c>
       <c r="B38" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494871</v>
+        <v>494847</v>
       </c>
       <c r="R38" t="n">
-        <v>6847013</v>
+        <v>6847046</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3864,32 +3864,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125920678</v>
+        <v>125920385</v>
       </c>
       <c r="B33" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494852</v>
+        <v>494890</v>
       </c>
       <c r="R33" t="n">
-        <v>6847042</v>
+        <v>6846985</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3961,32 +3961,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125920385</v>
+        <v>125920678</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494890</v>
+        <v>494852</v>
       </c>
       <c r="R34" t="n">
-        <v>6846985</v>
+        <v>6847042</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4061,7 +4061,7 @@
         <v>125920281</v>
       </c>
       <c r="B35" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>125921495</v>
       </c>
       <c r="B36" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>125920499</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>125920758</v>
       </c>
       <c r="B38" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>125921522</v>
       </c>
       <c r="B39" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>125920975</v>
       </c>
       <c r="B40" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>125920924</v>
       </c>
       <c r="B41" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>125921363</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>125921474</v>
       </c>
       <c r="B43" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -4252,32 +4252,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125920499</v>
+        <v>125920758</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>98341</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,13 +4287,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494871</v>
+        <v>494847</v>
       </c>
       <c r="R37" t="n">
-        <v>6847013</v>
+        <v>6847046</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4349,32 +4349,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125920758</v>
+        <v>125920499</v>
       </c>
       <c r="B38" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494847</v>
+        <v>494871</v>
       </c>
       <c r="R38" t="n">
-        <v>6847046</v>
+        <v>6847013</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3964,7 +3964,7 @@
         <v>125920678</v>
       </c>
       <c r="B34" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>125921495</v>
       </c>
       <c r="B36" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4252,32 +4252,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125920758</v>
+        <v>125920499</v>
       </c>
       <c r="B37" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,13 +4287,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494847</v>
+        <v>494871</v>
       </c>
       <c r="R37" t="n">
-        <v>6847046</v>
+        <v>6847013</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4349,32 +4349,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125920499</v>
+        <v>125920758</v>
       </c>
       <c r="B38" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494871</v>
+        <v>494847</v>
       </c>
       <c r="R38" t="n">
-        <v>6847013</v>
+        <v>6847046</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>125921522</v>
       </c>
       <c r="B39" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>125920975</v>
       </c>
       <c r="B40" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>125920924</v>
       </c>
       <c r="B41" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>125921474</v>
       </c>
       <c r="B43" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3864,32 +3864,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125920385</v>
+        <v>125920678</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494890</v>
+        <v>494852</v>
       </c>
       <c r="R33" t="n">
-        <v>6846985</v>
+        <v>6847042</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3961,32 +3961,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125920678</v>
+        <v>125920385</v>
       </c>
       <c r="B34" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494852</v>
+        <v>494890</v>
       </c>
       <c r="R34" t="n">
-        <v>6847042</v>
+        <v>6846985</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3864,32 +3864,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125920678</v>
+        <v>125920385</v>
       </c>
       <c r="B33" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494852</v>
+        <v>494890</v>
       </c>
       <c r="R33" t="n">
-        <v>6847042</v>
+        <v>6846985</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3961,32 +3961,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125920385</v>
+        <v>125920678</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494890</v>
+        <v>494852</v>
       </c>
       <c r="R34" t="n">
-        <v>6846985</v>
+        <v>6847042</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4158,7 +4158,7 @@
         <v>125921495</v>
       </c>
       <c r="B36" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4252,32 +4252,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125920499</v>
+        <v>125920758</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,13 +4287,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494871</v>
+        <v>494847</v>
       </c>
       <c r="R37" t="n">
-        <v>6847013</v>
+        <v>6847046</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4349,32 +4349,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125920758</v>
+        <v>125920499</v>
       </c>
       <c r="B38" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494847</v>
+        <v>494871</v>
       </c>
       <c r="R38" t="n">
-        <v>6847046</v>
+        <v>6847013</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>125921522</v>
       </c>
       <c r="B39" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>125920975</v>
       </c>
       <c r="B40" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>125920924</v>
       </c>
       <c r="B41" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>125921474</v>
       </c>
       <c r="B43" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -4252,32 +4252,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125920758</v>
+        <v>125920499</v>
       </c>
       <c r="B37" t="n">
-        <v>98345</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,13 +4287,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494847</v>
+        <v>494871</v>
       </c>
       <c r="R37" t="n">
-        <v>6847046</v>
+        <v>6847013</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4349,32 +4349,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125920499</v>
+        <v>125920758</v>
       </c>
       <c r="B38" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494871</v>
+        <v>494847</v>
       </c>
       <c r="R38" t="n">
-        <v>6847013</v>
+        <v>6847046</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3864,32 +3864,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125920385</v>
+        <v>125920678</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494890</v>
+        <v>494852</v>
       </c>
       <c r="R33" t="n">
-        <v>6846985</v>
+        <v>6847042</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3961,32 +3961,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125920678</v>
+        <v>125920385</v>
       </c>
       <c r="B34" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494852</v>
+        <v>494890</v>
       </c>
       <c r="R34" t="n">
-        <v>6847042</v>
+        <v>6846985</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4061,7 +4061,7 @@
         <v>125920281</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>125921495</v>
       </c>
       <c r="B36" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>125920499</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>125920758</v>
       </c>
       <c r="B38" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>125921522</v>
       </c>
       <c r="B39" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4543,10 +4543,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125920975</v>
+        <v>125920924</v>
       </c>
       <c r="B40" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494843</v>
+        <v>494851</v>
       </c>
       <c r="R40" t="n">
-        <v>6847097</v>
+        <v>6847070</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4640,10 +4640,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125920924</v>
+        <v>125920975</v>
       </c>
       <c r="B41" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494851</v>
+        <v>494843</v>
       </c>
       <c r="R41" t="n">
-        <v>6847070</v>
+        <v>6847097</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4740,7 +4740,7 @@
         <v>125921363</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>125921474</v>
       </c>
       <c r="B43" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -4543,7 +4543,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125920924</v>
+        <v>125920975</v>
       </c>
       <c r="B40" t="n">
         <v>98349</v>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494851</v>
+        <v>494843</v>
       </c>
       <c r="R40" t="n">
-        <v>6847070</v>
+        <v>6847097</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4640,7 +4640,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125920975</v>
+        <v>125920924</v>
       </c>
       <c r="B41" t="n">
         <v>98349</v>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494843</v>
+        <v>494851</v>
       </c>
       <c r="R41" t="n">
-        <v>6847097</v>
+        <v>6847070</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3864,32 +3864,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125920678</v>
+        <v>125920385</v>
       </c>
       <c r="B33" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494852</v>
+        <v>494890</v>
       </c>
       <c r="R33" t="n">
-        <v>6847042</v>
+        <v>6846985</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3961,32 +3961,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125920385</v>
+        <v>125920678</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494890</v>
+        <v>494852</v>
       </c>
       <c r="R34" t="n">
-        <v>6846985</v>
+        <v>6847042</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4158,7 +4158,7 @@
         <v>125921495</v>
       </c>
       <c r="B36" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>125920758</v>
       </c>
       <c r="B38" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>125921522</v>
       </c>
       <c r="B39" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>125920975</v>
       </c>
       <c r="B40" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>125920924</v>
       </c>
       <c r="B41" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>125921474</v>
       </c>
       <c r="B43" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -4252,32 +4252,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125920499</v>
+        <v>125920758</v>
       </c>
       <c r="B37" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,13 +4287,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494871</v>
+        <v>494847</v>
       </c>
       <c r="R37" t="n">
-        <v>6847013</v>
+        <v>6847046</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4349,32 +4349,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125920758</v>
+        <v>125920499</v>
       </c>
       <c r="B38" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494847</v>
+        <v>494871</v>
       </c>
       <c r="R38" t="n">
-        <v>6847046</v>
+        <v>6847013</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3867,7 +3867,7 @@
         <v>125920385</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>125920678</v>
       </c>
       <c r="B34" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>125920281</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>125921495</v>
       </c>
       <c r="B36" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4252,32 +4252,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125920758</v>
+        <v>125920499</v>
       </c>
       <c r="B37" t="n">
-        <v>98352</v>
+        <v>78980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,13 +4287,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494847</v>
+        <v>494871</v>
       </c>
       <c r="R37" t="n">
-        <v>6847046</v>
+        <v>6847013</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4349,32 +4349,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125920499</v>
+        <v>125920758</v>
       </c>
       <c r="B38" t="n">
-        <v>78977</v>
+        <v>98361</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494871</v>
+        <v>494847</v>
       </c>
       <c r="R38" t="n">
-        <v>6847013</v>
+        <v>6847046</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>125921522</v>
       </c>
       <c r="B39" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>125920975</v>
       </c>
       <c r="B40" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>125920924</v>
       </c>
       <c r="B41" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>125921363</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>125921474</v>
       </c>
       <c r="B43" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -3864,32 +3864,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125920385</v>
+        <v>125920678</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494890</v>
+        <v>494852</v>
       </c>
       <c r="R33" t="n">
-        <v>6846985</v>
+        <v>6847042</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3961,32 +3961,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125920678</v>
+        <v>125920385</v>
       </c>
       <c r="B34" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494852</v>
+        <v>494890</v>
       </c>
       <c r="R34" t="n">
-        <v>6847042</v>
+        <v>6846985</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -5037,32 +5037,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126668567</v>
+        <v>126669187</v>
       </c>
       <c r="B45" t="n">
-        <v>57817</v>
+        <v>98353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5072,13 +5072,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494848</v>
+        <v>494929</v>
       </c>
       <c r="R45" t="n">
-        <v>6847223</v>
+        <v>6847406</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5122,44 +5122,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126669187</v>
+        <v>126668515</v>
       </c>
       <c r="B46" t="n">
-        <v>98278</v>
+        <v>79011</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494929</v>
+        <v>494882</v>
       </c>
       <c r="R46" t="n">
-        <v>6847406</v>
+        <v>6847338</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126668515</v>
+        <v>126668567</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494882</v>
+        <v>494848</v>
       </c>
       <c r="R47" t="n">
-        <v>6847338</v>
+        <v>6847223</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5316,12 +5316,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5438,7 +5438,7 @@
         <v>126668408</v>
       </c>
       <c r="B49" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>126668480</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>126668263</v>
       </c>
       <c r="B52" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>126668560</v>
       </c>
       <c r="B53" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>126668632</v>
       </c>
       <c r="B54" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -5037,32 +5037,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126669187</v>
+        <v>126668567</v>
       </c>
       <c r="B45" t="n">
-        <v>98353</v>
+        <v>57817</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5072,13 +5072,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494929</v>
+        <v>494848</v>
       </c>
       <c r="R45" t="n">
-        <v>6847406</v>
+        <v>6847223</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5122,44 +5122,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126668515</v>
+        <v>126669187</v>
       </c>
       <c r="B46" t="n">
-        <v>79011</v>
+        <v>98359</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494882</v>
+        <v>494929</v>
       </c>
       <c r="R46" t="n">
-        <v>6847338</v>
+        <v>6847406</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126668567</v>
+        <v>126668515</v>
       </c>
       <c r="B47" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494848</v>
+        <v>494882</v>
       </c>
       <c r="R47" t="n">
-        <v>6847223</v>
+        <v>6847338</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5316,12 +5316,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5438,7 +5438,7 @@
         <v>126668408</v>
       </c>
       <c r="B49" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>126668480</v>
       </c>
       <c r="B50" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>126668263</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>126668560</v>
       </c>
       <c r="B53" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>126668632</v>
       </c>
       <c r="B54" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -5037,32 +5037,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126668567</v>
+        <v>126669187</v>
       </c>
       <c r="B45" t="n">
-        <v>57817</v>
+        <v>98359</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5072,13 +5072,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494848</v>
+        <v>494929</v>
       </c>
       <c r="R45" t="n">
-        <v>6847223</v>
+        <v>6847406</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5122,44 +5122,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126669187</v>
+        <v>126668515</v>
       </c>
       <c r="B46" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494929</v>
+        <v>494882</v>
       </c>
       <c r="R46" t="n">
-        <v>6847406</v>
+        <v>6847338</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126668515</v>
+        <v>126668567</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494882</v>
+        <v>494848</v>
       </c>
       <c r="R47" t="n">
-        <v>6847338</v>
+        <v>6847223</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5316,12 +5316,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -5037,32 +5037,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126669187</v>
+        <v>126668515</v>
       </c>
       <c r="B45" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494929</v>
+        <v>494882</v>
       </c>
       <c r="R45" t="n">
-        <v>6847406</v>
+        <v>6847338</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5134,10 +5134,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126668515</v>
+        <v>126668567</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5145,21 +5145,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5169,13 +5169,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494882</v>
+        <v>494848</v>
       </c>
       <c r="R46" t="n">
-        <v>6847338</v>
+        <v>6847223</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5219,44 +5219,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126668567</v>
+        <v>126669187</v>
       </c>
       <c r="B47" t="n">
-        <v>57817</v>
+        <v>98360</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494848</v>
+        <v>494929</v>
       </c>
       <c r="R47" t="n">
-        <v>6847223</v>
+        <v>6847406</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5316,12 +5316,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5438,7 +5438,7 @@
         <v>126668408</v>
       </c>
       <c r="B49" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>126668263</v>
       </c>
       <c r="B52" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>126668560</v>
       </c>
       <c r="B53" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -5037,32 +5037,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126668515</v>
+        <v>126669187</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494882</v>
+        <v>494929</v>
       </c>
       <c r="R45" t="n">
-        <v>6847338</v>
+        <v>6847406</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5134,10 +5134,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126668567</v>
+        <v>126668515</v>
       </c>
       <c r="B46" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5145,21 +5145,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5169,13 +5169,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494848</v>
+        <v>494882</v>
       </c>
       <c r="R46" t="n">
-        <v>6847223</v>
+        <v>6847338</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5219,44 +5219,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126669187</v>
+        <v>126668567</v>
       </c>
       <c r="B47" t="n">
-        <v>98360</v>
+        <v>57817</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494929</v>
+        <v>494848</v>
       </c>
       <c r="R47" t="n">
-        <v>6847406</v>
+        <v>6847223</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5316,12 +5316,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -5037,32 +5037,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126669187</v>
+        <v>126668515</v>
       </c>
       <c r="B45" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494929</v>
+        <v>494882</v>
       </c>
       <c r="R45" t="n">
-        <v>6847406</v>
+        <v>6847338</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5134,32 +5134,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126668515</v>
+        <v>126669187</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494882</v>
+        <v>494929</v>
       </c>
       <c r="R46" t="n">
-        <v>6847338</v>
+        <v>6847406</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -5037,32 +5037,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126668515</v>
+        <v>126669187</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>98353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494882</v>
+        <v>494929</v>
       </c>
       <c r="R45" t="n">
-        <v>6847338</v>
+        <v>6847406</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5134,32 +5134,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126669187</v>
+        <v>126668515</v>
       </c>
       <c r="B46" t="n">
-        <v>98360</v>
+        <v>79011</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494929</v>
+        <v>494882</v>
       </c>
       <c r="R46" t="n">
-        <v>6847406</v>
+        <v>6847338</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5331,7 +5331,7 @@
         <v>126669041</v>
       </c>
       <c r="B48" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>126668408</v>
       </c>
       <c r="B49" t="n">
-        <v>98360</v>
+        <v>98353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>126668480</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>126668464</v>
       </c>
       <c r="B51" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>126668263</v>
       </c>
       <c r="B52" t="n">
-        <v>98477</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>126668560</v>
       </c>
       <c r="B53" t="n">
-        <v>98360</v>
+        <v>98353</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>126668632</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -5331,7 +5331,7 @@
         <v>126669041</v>
       </c>
       <c r="B48" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>126668464</v>
       </c>
       <c r="B51" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123398345</v>
+        <v>123396886</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494856</v>
+        <v>494774</v>
       </c>
       <c r="R2" t="n">
-        <v>6847291</v>
+        <v>6847453</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,49 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123402561</v>
+        <v>123397848</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494857</v>
+        <v>494825</v>
       </c>
       <c r="R3" t="n">
-        <v>6847085</v>
+        <v>6847351</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123395626</v>
+        <v>123403597</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494727</v>
+        <v>494804</v>
       </c>
       <c r="R4" t="n">
-        <v>6847673</v>
+        <v>6847196</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123398134</v>
+        <v>123402474</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494855</v>
+        <v>494859</v>
       </c>
       <c r="R5" t="n">
-        <v>6847271</v>
+        <v>6847114</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123399650</v>
+        <v>123397886</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494916</v>
+        <v>494832</v>
       </c>
       <c r="R6" t="n">
-        <v>6847423</v>
+        <v>6847342</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123395990</v>
+        <v>123394705</v>
       </c>
       <c r="B7" t="n">
-        <v>78546</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494764</v>
+        <v>494712</v>
       </c>
       <c r="R7" t="n">
-        <v>6847568</v>
+        <v>6847772</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,31 +1245,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123398038</v>
+        <v>123395626</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1327,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494836</v>
+        <v>494727</v>
       </c>
       <c r="R8" t="n">
-        <v>6847308</v>
+        <v>6847673</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,31 +1342,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123398359</v>
+        <v>123395906</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1429,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494882</v>
+        <v>494732</v>
       </c>
       <c r="R9" t="n">
-        <v>6847247</v>
+        <v>6847579</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,49 +1439,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123403597</v>
+        <v>123398038</v>
       </c>
       <c r="B10" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494804</v>
+        <v>494836</v>
       </c>
       <c r="R10" t="n">
-        <v>6847196</v>
+        <v>6847308</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1593,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123396228</v>
+        <v>123398134</v>
       </c>
       <c r="B11" t="n">
-        <v>79399</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494766</v>
+        <v>494855</v>
       </c>
       <c r="R11" t="n">
-        <v>6847564</v>
+        <v>6847271</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123402845</v>
+        <v>123398345</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,46 +1656,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494845</v>
+        <v>494856</v>
       </c>
       <c r="R12" t="n">
-        <v>6847104</v>
+        <v>6847291</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123397886</v>
+        <v>123398359</v>
       </c>
       <c r="B13" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494832</v>
+        <v>494882</v>
       </c>
       <c r="R13" t="n">
-        <v>6847342</v>
+        <v>6847247</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1908,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123402870</v>
+        <v>123399373</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,34 +1850,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494829</v>
+        <v>494944</v>
       </c>
       <c r="R14" t="n">
-        <v>6847079</v>
+        <v>6847470</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,27 +1924,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123402463</v>
+        <v>123399584</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2026,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494846</v>
+        <v>494901</v>
       </c>
       <c r="R15" t="n">
-        <v>6847218</v>
+        <v>6847454</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2112,53 +2033,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123395505</v>
+        <v>123399860</v>
       </c>
       <c r="B16" t="n">
-        <v>78547</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494727</v>
+        <v>494841</v>
       </c>
       <c r="R16" t="n">
-        <v>6847677</v>
+        <v>6847322</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2202,49 +2118,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123397848</v>
+        <v>123399903</v>
       </c>
       <c r="B17" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,13 +2165,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494825</v>
+        <v>494805</v>
       </c>
       <c r="R17" t="n">
-        <v>6847351</v>
+        <v>6847310</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2316,53 +2227,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123403076</v>
+        <v>125920281</v>
       </c>
       <c r="B18" t="n">
-        <v>79920</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494829</v>
+        <v>494845</v>
       </c>
       <c r="R18" t="n">
-        <v>6847079</v>
+        <v>6846968</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2386,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,31 +2312,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123399860</v>
+        <v>125920385</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2458,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494841</v>
+        <v>494890</v>
       </c>
       <c r="R19" t="n">
-        <v>6847322</v>
+        <v>6846985</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2488,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2520,19 +2421,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123399373</v>
+        <v>125920499</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2560,13 +2456,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494944</v>
+        <v>494871</v>
       </c>
       <c r="R20" t="n">
-        <v>6847470</v>
+        <v>6847013</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2590,12 +2486,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2622,53 +2518,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123402474</v>
+        <v>125921363</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494859</v>
+        <v>494825</v>
       </c>
       <c r="R21" t="n">
-        <v>6847114</v>
+        <v>6847192</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2692,12 +2583,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2712,65 +2603,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123398723</v>
+        <v>126668361</v>
       </c>
       <c r="B22" t="n">
-        <v>78546</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494908</v>
+        <v>494800</v>
       </c>
       <c r="R22" t="n">
-        <v>6847305</v>
+        <v>6847362</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2794,12 +2680,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2814,31 +2700,26 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123395906</v>
+        <v>126668480</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2862,14 +2743,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494732</v>
+        <v>494850</v>
       </c>
       <c r="R23" t="n">
-        <v>6847579</v>
+        <v>6847364</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2896,12 +2777,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2928,53 +2809,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123396986</v>
+        <v>126668515</v>
       </c>
       <c r="B24" t="n">
-        <v>78547</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494778</v>
+        <v>494882</v>
       </c>
       <c r="R24" t="n">
-        <v>6847448</v>
+        <v>6847338</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2998,12 +2874,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3018,49 +2894,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123397955</v>
+        <v>126668632</v>
       </c>
       <c r="B25" t="n">
-        <v>78547</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494834</v>
+        <v>494936</v>
       </c>
       <c r="R25" t="n">
-        <v>6847337</v>
+        <v>6847305</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3100,12 +2971,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3132,15 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123398955</v>
+        <v>123395990</v>
       </c>
       <c r="B26" t="n">
-        <v>78546</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3172,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494898</v>
+        <v>494764</v>
       </c>
       <c r="R26" t="n">
-        <v>6847337</v>
+        <v>6847568</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3234,15 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123395955</v>
+        <v>123398597</v>
       </c>
       <c r="B27" t="n">
-        <v>78547</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494764</v>
+        <v>494911</v>
       </c>
       <c r="R27" t="n">
-        <v>6847568</v>
+        <v>6847281</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3336,15 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123396886</v>
+        <v>123398723</v>
       </c>
       <c r="B28" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,13 +3232,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494774</v>
+        <v>494908</v>
       </c>
       <c r="R28" t="n">
-        <v>6847453</v>
+        <v>6847305</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3438,53 +3294,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124432056</v>
+        <v>123398955</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494859</v>
+        <v>494898</v>
       </c>
       <c r="R29" t="n">
-        <v>6847061</v>
+        <v>6847337</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3508,12 +3359,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3528,71 +3379,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124431969</v>
+        <v>124431907</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494837</v>
+        <v>494819</v>
       </c>
       <c r="R30" t="n">
-        <v>6847108</v>
+        <v>6847117</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3651,53 +3488,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124431907</v>
+        <v>123399650</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494819</v>
+        <v>494916</v>
       </c>
       <c r="R31" t="n">
-        <v>6847117</v>
+        <v>6847423</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3721,12 +3553,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3741,74 +3573,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124432127</v>
+        <v>123403076</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494854</v>
+        <v>494829</v>
       </c>
       <c r="R32" t="n">
-        <v>6847009</v>
+        <v>6847079</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3832,12 +3650,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3852,60 +3670,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125920678</v>
+        <v>123395370</v>
       </c>
       <c r="B33" t="n">
-        <v>98361</v>
+        <v>80468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494852</v>
+        <v>494741</v>
       </c>
       <c r="R33" t="n">
-        <v>6847042</v>
+        <v>6847717</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3929,12 +3747,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3949,22 +3767,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125920385</v>
+        <v>126668464</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3972,34 +3790,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494890</v>
+        <v>494828</v>
       </c>
       <c r="R34" t="n">
-        <v>6846985</v>
+        <v>6847351</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4026,12 +3849,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4058,10 +3886,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125920281</v>
+        <v>126669041</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4069,34 +3897,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494845</v>
+        <v>494963</v>
       </c>
       <c r="R35" t="n">
-        <v>6846968</v>
+        <v>6847469</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4123,12 +3956,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4155,45 +3993,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125921495</v>
+        <v>126668047</v>
       </c>
       <c r="B36" t="n">
-        <v>98361</v>
+        <v>58114</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Kanallugnet, Kanallugnet, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494839</v>
+        <v>494668</v>
       </c>
       <c r="R36" t="n">
-        <v>6847211</v>
+        <v>6847411</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4220,12 +4058,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4252,10 +4090,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125920499</v>
+        <v>126668271</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>58114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4263,34 +4101,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Kanallugnet, Kanallugnet, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494871</v>
+        <v>494781</v>
       </c>
       <c r="R37" t="n">
-        <v>6847013</v>
+        <v>6847328</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4317,12 +4155,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4349,32 +4187,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125920758</v>
+        <v>126668567</v>
       </c>
       <c r="B38" t="n">
-        <v>98361</v>
+        <v>58114</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4384,10 +4222,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494847</v>
+        <v>494848</v>
       </c>
       <c r="R38" t="n">
-        <v>6847046</v>
+        <v>6847223</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4414,12 +4252,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4434,44 +4272,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125921522</v>
+        <v>126668408</v>
       </c>
       <c r="B39" t="n">
-        <v>98361</v>
+        <v>99035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4481,13 +4319,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494840</v>
+        <v>494805</v>
       </c>
       <c r="R39" t="n">
-        <v>6847209</v>
+        <v>6847258</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4511,12 +4349,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4531,44 +4369,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125920975</v>
+        <v>126668560</v>
       </c>
       <c r="B40" t="n">
-        <v>98361</v>
+        <v>99035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4578,13 +4416,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494843</v>
+        <v>494848</v>
       </c>
       <c r="R40" t="n">
-        <v>6847097</v>
+        <v>6847223</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4608,12 +4446,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4628,44 +4466,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125920924</v>
+        <v>126668651</v>
       </c>
       <c r="B41" t="n">
-        <v>98361</v>
+        <v>99035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4675,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494851</v>
+        <v>494941</v>
       </c>
       <c r="R41" t="n">
-        <v>6847070</v>
+        <v>6847303</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4705,12 +4543,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4737,32 +4575,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125921363</v>
+        <v>126669187</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>99035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4772,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494825</v>
+        <v>494929</v>
       </c>
       <c r="R42" t="n">
-        <v>6847192</v>
+        <v>6847406</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4802,12 +4640,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4834,57 +4672,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125921474</v>
+        <v>126669234</v>
       </c>
       <c r="B43" t="n">
-        <v>98361</v>
+        <v>99035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494832</v>
+        <v>494746</v>
       </c>
       <c r="R43" t="n">
-        <v>6847214</v>
+        <v>6847508</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4908,12 +4737,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4928,60 +4757,69 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126668047</v>
+        <v>126669264</v>
       </c>
       <c r="B44" t="n">
-        <v>57817</v>
+        <v>99142</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>219847</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kanallugnet, Kanallugnet, Hls</t>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494668</v>
+        <v>494750</v>
       </c>
       <c r="R44" t="n">
-        <v>6847411</v>
+        <v>6847534</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5025,60 +4863,69 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126668515</v>
+        <v>126669400</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>99142</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494882</v>
+        <v>494750</v>
       </c>
       <c r="R45" t="n">
-        <v>6847338</v>
+        <v>6847538</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5122,22 +4969,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126669187</v>
+        <v>126669422</v>
       </c>
       <c r="B46" t="n">
-        <v>98360</v>
+        <v>99142</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5145,37 +4992,46 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494929</v>
+        <v>494750</v>
       </c>
       <c r="R46" t="n">
-        <v>6847406</v>
+        <v>6847537</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5219,44 +5075,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126668567</v>
+        <v>126668263</v>
       </c>
       <c r="B47" t="n">
-        <v>57817</v>
+        <v>99153</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>219874</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5266,13 +5122,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494848</v>
+        <v>494777</v>
       </c>
       <c r="R47" t="n">
-        <v>6847223</v>
+        <v>6847301</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5328,50 +5184,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126669041</v>
+        <v>126669086</v>
       </c>
       <c r="B48" t="n">
-        <v>57852</v>
+        <v>99153</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494963</v>
+        <v>494951</v>
       </c>
       <c r="R48" t="n">
-        <v>6847469</v>
+        <v>6847478</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5404,11 +5255,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5435,48 +5281,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126668408</v>
+        <v>123395004</v>
       </c>
       <c r="B49" t="n">
-        <v>98360</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494805</v>
+        <v>494686</v>
       </c>
       <c r="R49" t="n">
-        <v>6847258</v>
+        <v>6847769</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5500,12 +5346,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5532,48 +5378,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126668480</v>
+        <v>123402463</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494850</v>
+        <v>494846</v>
       </c>
       <c r="R50" t="n">
-        <v>6847364</v>
+        <v>6847218</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5597,12 +5443,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5617,65 +5463,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126668464</v>
+        <v>123402561</v>
       </c>
       <c r="B51" t="n">
-        <v>57852</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494828</v>
+        <v>494857</v>
       </c>
       <c r="R51" t="n">
-        <v>6847351</v>
+        <v>6847085</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5699,17 +5540,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack.</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5724,60 +5560,69 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126668263</v>
+        <v>123402845</v>
       </c>
       <c r="B52" t="n">
-        <v>98477</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494777</v>
+        <v>494845</v>
       </c>
       <c r="R52" t="n">
-        <v>6847301</v>
+        <v>6847104</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5801,12 +5646,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5821,57 +5666,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126668560</v>
+        <v>123402870</v>
       </c>
       <c r="B53" t="n">
-        <v>98360</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494848</v>
+        <v>494829</v>
       </c>
       <c r="R53" t="n">
-        <v>6847223</v>
+        <v>6847079</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5898,12 +5743,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5930,45 +5775,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126668632</v>
+        <v>124431969</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494936</v>
+        <v>494837</v>
       </c>
       <c r="R54" t="n">
-        <v>6847305</v>
+        <v>6847108</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5995,12 +5849,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6024,6 +5878,1479 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>124432056</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>494859</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6847061</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>124432127</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>494854</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6847009</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125920678</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>494852</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6847042</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125920758</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>494847</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6847046</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125920924</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>494851</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6847070</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125920975</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>494843</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6847097</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125921474</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>494832</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6847214</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125921495</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>494839</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6847211</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125921522</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>494840</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6847209</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126668265</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kanallugnet, Kanallugnet, Hls</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>494780</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6847333</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>123395505</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>494727</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6847677</v>
+      </c>
+      <c r="S65" t="n">
+        <v>20</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>123395955</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>494764</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6847568</v>
+      </c>
+      <c r="S66" t="n">
+        <v>20</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>123396986</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>494778</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6847448</v>
+      </c>
+      <c r="S67" t="n">
+        <v>20</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>123397955</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Voxnans naturreservat, Voxnans naturreservat, Hls</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>494834</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6847337</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>123396228</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Rullbokanalen, Rullbokanalen, Hls</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>494766</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6847564</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3180-2025 artfynd.xlsx
+++ b/artfynd/A 3180-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123396886</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123397848</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403597</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402474</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123397886</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123394705</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123395626</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123395906</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123398038</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123398134</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123398345</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123398359</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123399373</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123399584</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123399860</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123399903</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125920281</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125920385</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125920499</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125921363</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126668361</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126668480</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126668515</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126668632</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123395990</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123398597</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123398723</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123398955</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124431907</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123399650</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123403076</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123395370</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3883,6 +4048,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126668464</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3990,6 +4160,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126669041</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4087,6 +4262,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126668047</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4184,6 +4364,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126668271</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4281,6 +4466,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126668567</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4378,6 +4568,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126668408</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4475,6 +4670,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126668560</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4572,6 +4772,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126668651</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4669,6 +4874,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126669187</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4766,6 +4976,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126669234</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4872,6 +5087,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126669264</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4978,6 +5198,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126669400</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5084,6 +5309,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126669422</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5181,6 +5411,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126668263</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5278,6 +5513,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126669086</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5375,6 +5615,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123395004</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5472,6 +5717,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402463</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5569,6 +5819,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402561</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5675,6 +5930,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402845</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5772,6 +6032,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123402870</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5878,6 +6143,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124431969</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5975,6 +6245,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432056</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6081,6 +6356,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432127</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6178,6 +6458,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125920678</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6275,6 +6560,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125920758</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6372,6 +6662,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125920924</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6469,6 +6764,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125920975</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6575,6 +6875,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125921474</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6672,6 +6977,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125921495</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6769,6 +7079,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125921522</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6866,6 +7181,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126668265</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6963,6 +7283,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123395505</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7060,6 +7385,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123395955</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7157,6 +7487,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123396986</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7254,6 +7589,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123397955</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7351,8 +7691,83 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123396228</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>